--- a/research/traditional_assets/database/data/lithuania/lithuania_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_paper_forest_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08212319963045958</v>
+        <v>0.08203826483101388</v>
       </c>
       <c r="C2">
-        <v>151.9979443410109</v>
+        <v>150.8051666649249</v>
       </c>
       <c r="D2">
-        <v>139.6979443410109</v>
+        <v>140.0253666649249</v>
       </c>
       <c r="E2">
-        <v>-9.220000000000001</v>
+        <v>-7.699800000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.5202</v>
       </c>
       <c r="G2">
         <v>12.3</v>
@@ -1451,28 +1451,28 @@
         <v>23</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07646606</v>
       </c>
       <c r="N2">
-        <v>23</v>
+        <v>22.92353394</v>
       </c>
       <c r="O2">
-        <v>3.45</v>
+        <v>3.438530091</v>
       </c>
       <c r="P2">
-        <v>19.55</v>
+        <v>19.485003849</v>
       </c>
       <c r="Q2">
-        <v>29.15</v>
+        <v>29.085003849</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08212319963045958</v>
+        <v>0.08243506548587261</v>
       </c>
       <c r="T2">
-        <v>0.6652721574126822</v>
+        <v>0.6709840900773365</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>300.7870419896095</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08203826483101388</v>
+        <v>0.08195333003156818</v>
       </c>
       <c r="C3">
-        <v>150.8051666649249</v>
+        <v>149.6139274114069</v>
       </c>
       <c r="D3">
-        <v>140.0253666649249</v>
+        <v>140.3543274114069</v>
       </c>
       <c r="E3">
-        <v>-7.699800000000001</v>
+        <v>-6.179600000000001</v>
       </c>
       <c r="F3">
-        <v>1.5202</v>
+        <v>3.0404</v>
       </c>
       <c r="G3">
         <v>12.3</v>
@@ -1533,28 +1533,28 @@
         <v>23</v>
       </c>
       <c r="M3">
-        <v>0.07646606</v>
+        <v>0.15293212</v>
       </c>
       <c r="N3">
-        <v>22.92353394</v>
+        <v>22.84706788</v>
       </c>
       <c r="O3">
-        <v>3.438530091</v>
+        <v>3.427060182</v>
       </c>
       <c r="P3">
-        <v>19.485003849</v>
+        <v>19.420007698</v>
       </c>
       <c r="Q3">
-        <v>29.085003849</v>
+        <v>29.020007698</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08243506548587261</v>
+        <v>0.08275329595057979</v>
       </c>
       <c r="T3">
-        <v>0.6709840900773365</v>
+        <v>0.6768125927963716</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>300.7870419896095</v>
+        <v>150.3935209948048</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08195333003156818</v>
+        <v>0.0818683952321225</v>
       </c>
       <c r="C4">
-        <v>149.6139274114069</v>
+        <v>148.4242374486099</v>
       </c>
       <c r="D4">
-        <v>140.3543274114069</v>
+        <v>140.6848374486099</v>
       </c>
       <c r="E4">
-        <v>-6.179600000000001</v>
+        <v>-4.659400000000001</v>
       </c>
       <c r="F4">
-        <v>3.0404</v>
+        <v>4.5606</v>
       </c>
       <c r="G4">
         <v>12.3</v>
@@ -1615,28 +1615,28 @@
         <v>23</v>
       </c>
       <c r="M4">
-        <v>0.15293212</v>
+        <v>0.22939818</v>
       </c>
       <c r="N4">
-        <v>22.84706788</v>
+        <v>22.77060182</v>
       </c>
       <c r="O4">
-        <v>3.427060182</v>
+        <v>3.415590273</v>
       </c>
       <c r="P4">
-        <v>19.420007698</v>
+        <v>19.355011547</v>
       </c>
       <c r="Q4">
-        <v>29.020007698</v>
+        <v>28.955011547</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08275329595057979</v>
+        <v>0.08307808786816753</v>
       </c>
       <c r="T4">
-        <v>0.6768125927963716</v>
+        <v>0.6827612708292011</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>150.3935209948048</v>
+        <v>100.2623473298698</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0818683952321225</v>
+        <v>0.08178346043267681</v>
       </c>
       <c r="C5">
-        <v>148.4242374486099</v>
+        <v>147.236107747299</v>
       </c>
       <c r="D5">
-        <v>140.6848374486099</v>
+        <v>141.016907747299</v>
       </c>
       <c r="E5">
-        <v>-4.659400000000001</v>
+        <v>-3.1392</v>
       </c>
       <c r="F5">
-        <v>4.5606</v>
+        <v>6.080800000000001</v>
       </c>
       <c r="G5">
         <v>12.3</v>
@@ -1697,28 +1697,28 @@
         <v>23</v>
       </c>
       <c r="M5">
-        <v>0.22939818</v>
+        <v>0.30586424</v>
       </c>
       <c r="N5">
-        <v>22.77060182</v>
+        <v>22.69413576</v>
       </c>
       <c r="O5">
-        <v>3.415590273</v>
+        <v>3.404120364</v>
       </c>
       <c r="P5">
-        <v>19.355011547</v>
+        <v>19.290015396</v>
       </c>
       <c r="Q5">
-        <v>28.955011547</v>
+        <v>28.890015396</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08307808786816753</v>
+        <v>0.08340964628403835</v>
       </c>
       <c r="T5">
-        <v>0.6827612708292011</v>
+        <v>0.6888338796543814</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>100.2623473298698</v>
+        <v>75.19676049740238</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08178346043267681</v>
+        <v>0.08169852563323111</v>
       </c>
       <c r="C6">
-        <v>147.236107747299</v>
+        <v>146.0495493820653</v>
       </c>
       <c r="D6">
-        <v>141.016907747299</v>
+        <v>141.3505493820653</v>
       </c>
       <c r="E6">
-        <v>-3.1392</v>
+        <v>-1.619</v>
       </c>
       <c r="F6">
-        <v>6.080800000000001</v>
+        <v>7.601000000000001</v>
       </c>
       <c r="G6">
         <v>12.3</v>
@@ -1779,28 +1779,28 @@
         <v>23</v>
       </c>
       <c r="M6">
-        <v>0.30586424</v>
+        <v>0.3823303</v>
       </c>
       <c r="N6">
-        <v>22.69413576</v>
+        <v>22.6176697</v>
       </c>
       <c r="O6">
-        <v>3.404120364</v>
+        <v>3.392650455</v>
       </c>
       <c r="P6">
-        <v>19.290015396</v>
+        <v>19.225019245</v>
       </c>
       <c r="Q6">
-        <v>28.890015396</v>
+        <v>28.825019245</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08340964628403835</v>
+        <v>0.08374818487708539</v>
       </c>
       <c r="T6">
-        <v>0.6888338796543814</v>
+        <v>0.6950343328758811</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>75.19676049740238</v>
+        <v>60.1574083979219</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08169852563323111</v>
+        <v>0.08161359083378544</v>
       </c>
       <c r="C7">
-        <v>146.0495493820653</v>
+        <v>144.8645735325567</v>
       </c>
       <c r="D7">
-        <v>141.3505493820653</v>
+        <v>141.6857735325567</v>
       </c>
       <c r="E7">
-        <v>-1.619</v>
+        <v>-0.09879999999999889</v>
       </c>
       <c r="F7">
-        <v>7.601000000000001</v>
+        <v>9.121200000000002</v>
       </c>
       <c r="G7">
         <v>12.3</v>
@@ -1861,28 +1861,28 @@
         <v>23</v>
       </c>
       <c r="M7">
-        <v>0.3823303</v>
+        <v>0.4587963600000001</v>
       </c>
       <c r="N7">
-        <v>22.6176697</v>
+        <v>22.54120364</v>
       </c>
       <c r="O7">
-        <v>3.392650455</v>
+        <v>3.381180546</v>
       </c>
       <c r="P7">
-        <v>19.225019245</v>
+        <v>19.160023094</v>
       </c>
       <c r="Q7">
-        <v>28.825019245</v>
+        <v>28.760023094</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08374818487708539</v>
+        <v>0.08409392641892068</v>
       </c>
       <c r="T7">
-        <v>0.6950343328758811</v>
+        <v>0.7013667106340086</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>60.1574083979219</v>
+        <v>50.13117366493491</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08161359083378544</v>
+        <v>0.08152865603433976</v>
       </c>
       <c r="C8">
-        <v>144.8645735325567</v>
+        <v>143.6811914847273</v>
       </c>
       <c r="D8">
-        <v>141.6857735325567</v>
+        <v>142.0225914847273</v>
       </c>
       <c r="E8">
-        <v>-0.09880000000000067</v>
+        <v>1.421399999999998</v>
       </c>
       <c r="F8">
-        <v>9.1212</v>
+        <v>10.6414</v>
       </c>
       <c r="G8">
         <v>12.3</v>
@@ -1943,28 +1943,28 @@
         <v>23</v>
       </c>
       <c r="M8">
-        <v>0.45879636</v>
+        <v>0.5352624199999999</v>
       </c>
       <c r="N8">
-        <v>22.54120364</v>
+        <v>22.46473758</v>
       </c>
       <c r="O8">
-        <v>3.381180546</v>
+        <v>3.369710637</v>
       </c>
       <c r="P8">
-        <v>19.160023094</v>
+        <v>19.095026943</v>
       </c>
       <c r="Q8">
-        <v>28.760023094</v>
+        <v>28.695026943</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08409392641892068</v>
+        <v>0.08444710326273092</v>
       </c>
       <c r="T8">
-        <v>0.7013667106340086</v>
+        <v>0.7078352685589775</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>50.13117366493492</v>
+        <v>42.96957742708708</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08152865603433976</v>
+        <v>0.08144372123489406</v>
       </c>
       <c r="C9">
-        <v>143.6811914847273</v>
+        <v>142.4994146321035</v>
       </c>
       <c r="D9">
-        <v>142.0225914847273</v>
+        <v>142.3610146321035</v>
       </c>
       <c r="E9">
-        <v>1.4214</v>
+        <v>2.941600000000001</v>
       </c>
       <c r="F9">
-        <v>10.6414</v>
+        <v>12.1616</v>
       </c>
       <c r="G9">
         <v>12.3</v>
@@ -2025,28 +2025,28 @@
         <v>23</v>
       </c>
       <c r="M9">
-        <v>0.53526242</v>
+        <v>0.61172848</v>
       </c>
       <c r="N9">
-        <v>22.46473758</v>
+        <v>22.38827152</v>
       </c>
       <c r="O9">
-        <v>3.369710637</v>
+        <v>3.358240728</v>
       </c>
       <c r="P9">
-        <v>19.095026943</v>
+        <v>19.030030792</v>
       </c>
       <c r="Q9">
-        <v>28.695026943</v>
+        <v>28.630030792</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08444710326273092</v>
+        <v>0.08480795786401528</v>
       </c>
       <c r="T9">
-        <v>0.7078352685589775</v>
+        <v>0.7144444473084022</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>42.96957742708707</v>
+        <v>37.59838024870119</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08144372123489406</v>
+        <v>0.08135878643544839</v>
       </c>
       <c r="C10">
-        <v>142.4994146321035</v>
+        <v>141.3192544770687</v>
       </c>
       <c r="D10">
-        <v>142.3610146321035</v>
+        <v>142.7010544770687</v>
       </c>
       <c r="E10">
-        <v>2.941600000000001</v>
+        <v>4.4618</v>
       </c>
       <c r="F10">
-        <v>12.1616</v>
+        <v>13.6818</v>
       </c>
       <c r="G10">
         <v>12.3</v>
@@ -2107,28 +2107,28 @@
         <v>23</v>
       </c>
       <c r="M10">
-        <v>0.61172848</v>
+        <v>0.68819454</v>
       </c>
       <c r="N10">
-        <v>22.38827152</v>
+        <v>22.31180546</v>
       </c>
       <c r="O10">
-        <v>3.358240728</v>
+        <v>3.346770819</v>
       </c>
       <c r="P10">
-        <v>19.030030792</v>
+        <v>18.965034641</v>
       </c>
       <c r="Q10">
-        <v>28.630030792</v>
+        <v>28.565034641</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08480795786401528</v>
+        <v>0.08517674333565756</v>
       </c>
       <c r="T10">
-        <v>0.7144444473084022</v>
+        <v>0.7211988827336384</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>37.59838024870119</v>
+        <v>33.42078244328994</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08135878643544839</v>
+        <v>0.08127385163600268</v>
       </c>
       <c r="C11">
-        <v>141.3192544770687</v>
+        <v>140.1407226321669</v>
       </c>
       <c r="D11">
-        <v>142.7010544770687</v>
+        <v>143.0427226321669</v>
       </c>
       <c r="E11">
-        <v>4.4618</v>
+        <v>5.981999999999999</v>
       </c>
       <c r="F11">
-        <v>13.6818</v>
+        <v>15.202</v>
       </c>
       <c r="G11">
         <v>12.3</v>
@@ -2189,28 +2189,28 @@
         <v>23</v>
       </c>
       <c r="M11">
-        <v>0.68819454</v>
+        <v>0.7646605999999999</v>
       </c>
       <c r="N11">
-        <v>22.31180546</v>
+        <v>22.2353394</v>
       </c>
       <c r="O11">
-        <v>3.346770819</v>
+        <v>3.33530091</v>
       </c>
       <c r="P11">
-        <v>18.965034641</v>
+        <v>18.90003849</v>
       </c>
       <c r="Q11">
-        <v>28.565034641</v>
+        <v>28.50003849</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08517674333565756</v>
+        <v>0.08555372404000297</v>
       </c>
       <c r="T11">
-        <v>0.7211988827336384</v>
+        <v>0.72810341672388</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>33.42078244328994</v>
+        <v>30.07870419896096</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08127385163600268</v>
+        <v>0.08118891683655699</v>
       </c>
       <c r="C12">
-        <v>140.1407226321669</v>
+        <v>138.963830821424</v>
       </c>
       <c r="D12">
-        <v>143.0427226321669</v>
+        <v>143.386030821424</v>
       </c>
       <c r="E12">
-        <v>5.982000000000001</v>
+        <v>7.5022</v>
       </c>
       <c r="F12">
-        <v>15.202</v>
+        <v>16.7222</v>
       </c>
       <c r="G12">
         <v>12.3</v>
@@ -2271,28 +2271,28 @@
         <v>23</v>
       </c>
       <c r="M12">
-        <v>0.7646606</v>
+        <v>0.84112666</v>
       </c>
       <c r="N12">
-        <v>22.2353394</v>
+        <v>22.15887334</v>
       </c>
       <c r="O12">
-        <v>3.33530091</v>
+        <v>3.323831001</v>
       </c>
       <c r="P12">
-        <v>18.90003849</v>
+        <v>18.835042339</v>
       </c>
       <c r="Q12">
-        <v>28.50003849</v>
+        <v>28.435042339</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08555372404000297</v>
+        <v>0.08593917622085055</v>
       </c>
       <c r="T12">
-        <v>0.72810341672388</v>
+        <v>0.735163108781318</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>30.07870419896095</v>
+        <v>27.34427654450995</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08118891683655699</v>
+        <v>0.08110398203711131</v>
       </c>
       <c r="C13">
-        <v>138.963830821424</v>
+        <v>137.7885908816894</v>
       </c>
       <c r="D13">
-        <v>143.386030821424</v>
+        <v>143.7309908816894</v>
       </c>
       <c r="E13">
-        <v>7.5022</v>
+        <v>9.022399999999999</v>
       </c>
       <c r="F13">
-        <v>16.7222</v>
+        <v>18.2424</v>
       </c>
       <c r="G13">
         <v>12.3</v>
@@ -2353,28 +2353,28 @@
         <v>23</v>
       </c>
       <c r="M13">
-        <v>0.84112666</v>
+        <v>0.9175927199999999</v>
       </c>
       <c r="N13">
-        <v>22.15887334</v>
+        <v>22.08240728</v>
       </c>
       <c r="O13">
-        <v>3.323831001</v>
+        <v>3.312361092</v>
       </c>
       <c r="P13">
-        <v>18.835042339</v>
+        <v>18.770046188</v>
       </c>
       <c r="Q13">
-        <v>28.435042339</v>
+        <v>28.370046188</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08593917622085055</v>
+        <v>0.08633338867853557</v>
       </c>
       <c r="T13">
-        <v>0.735163108781318</v>
+        <v>0.7423832483855158</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>27.34427654450995</v>
+        <v>25.06558683246746</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08110398203711131</v>
+        <v>0.08101904723766561</v>
       </c>
       <c r="C14">
-        <v>137.7885908816894</v>
+        <v>136.6150147639962</v>
       </c>
       <c r="D14">
-        <v>143.7309908816894</v>
+        <v>144.0776147639962</v>
       </c>
       <c r="E14">
-        <v>9.022399999999999</v>
+        <v>10.5426</v>
       </c>
       <c r="F14">
-        <v>18.2424</v>
+        <v>19.7626</v>
       </c>
       <c r="G14">
         <v>12.3</v>
@@ -2435,28 +2435,28 @@
         <v>23</v>
       </c>
       <c r="M14">
-        <v>0.9175927199999999</v>
+        <v>0.99405878</v>
       </c>
       <c r="N14">
-        <v>22.08240728</v>
+        <v>22.00594122</v>
       </c>
       <c r="O14">
-        <v>3.312361092</v>
+        <v>3.300891183</v>
       </c>
       <c r="P14">
-        <v>18.770046188</v>
+        <v>18.705050037</v>
       </c>
       <c r="Q14">
-        <v>28.370046188</v>
+        <v>28.305050037</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08633338867853557</v>
+        <v>0.08673666349156967</v>
       </c>
       <c r="T14">
-        <v>0.7423832483855158</v>
+        <v>0.7497693682104999</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.06558683246746</v>
+        <v>23.1374647684315</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08101904723766561</v>
+        <v>0.08093411243821991</v>
       </c>
       <c r="C15">
-        <v>136.6150147639962</v>
+        <v>135.4431145349415</v>
       </c>
       <c r="D15">
-        <v>144.0776147639962</v>
+        <v>144.4259145349415</v>
       </c>
       <c r="E15">
-        <v>10.5426</v>
+        <v>12.0628</v>
       </c>
       <c r="F15">
-        <v>19.7626</v>
+        <v>21.2828</v>
       </c>
       <c r="G15">
         <v>12.3</v>
@@ -2517,28 +2517,28 @@
         <v>23</v>
       </c>
       <c r="M15">
-        <v>0.99405878</v>
+        <v>1.07052484</v>
       </c>
       <c r="N15">
-        <v>22.00594122</v>
+        <v>21.92947516</v>
       </c>
       <c r="O15">
-        <v>3.300891183</v>
+        <v>3.289421274</v>
       </c>
       <c r="P15">
-        <v>18.705050037</v>
+        <v>18.640053886</v>
       </c>
       <c r="Q15">
-        <v>28.305050037</v>
+        <v>28.240053886</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08673666349156967</v>
+        <v>0.08714931678862781</v>
       </c>
       <c r="T15">
-        <v>0.7497693682104999</v>
+        <v>0.7573272582639718</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.1374647684315</v>
+        <v>21.48478871354353</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08093411243821991</v>
+        <v>0.08084917763877422</v>
       </c>
       <c r="C16">
-        <v>135.4431145349415</v>
+        <v>134.272902378086</v>
       </c>
       <c r="D16">
-        <v>144.4259145349415</v>
+        <v>144.775902378086</v>
       </c>
       <c r="E16">
-        <v>12.0628</v>
+        <v>13.583</v>
       </c>
       <c r="F16">
-        <v>21.2828</v>
+        <v>22.803</v>
       </c>
       <c r="G16">
         <v>12.3</v>
@@ -2599,28 +2599,28 @@
         <v>23</v>
       </c>
       <c r="M16">
-        <v>1.07052484</v>
+        <v>1.1469909</v>
       </c>
       <c r="N16">
-        <v>21.92947516</v>
+        <v>21.8530091</v>
       </c>
       <c r="O16">
-        <v>3.289421274</v>
+        <v>3.277951365</v>
       </c>
       <c r="P16">
-        <v>18.640053886</v>
+        <v>18.575057735</v>
       </c>
       <c r="Q16">
-        <v>28.240053886</v>
+        <v>28.175057735</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08714931678862781</v>
+        <v>0.08757167957502851</v>
       </c>
       <c r="T16">
-        <v>0.7573272582639718</v>
+        <v>0.7650629810245845</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.48478871354353</v>
+        <v>20.05246946597396</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08084917763877422</v>
+        <v>0.08076424283932854</v>
       </c>
       <c r="C17">
-        <v>134.272902378086</v>
+        <v>133.1043905953758</v>
       </c>
       <c r="D17">
-        <v>144.775902378086</v>
+        <v>145.1275905953758</v>
       </c>
       <c r="E17">
-        <v>13.583</v>
+        <v>15.1032</v>
       </c>
       <c r="F17">
-        <v>22.803</v>
+        <v>24.3232</v>
       </c>
       <c r="G17">
         <v>12.3</v>
@@ -2681,28 +2681,28 @@
         <v>23</v>
       </c>
       <c r="M17">
-        <v>1.1469909</v>
+        <v>1.22345696</v>
       </c>
       <c r="N17">
-        <v>21.8530091</v>
+        <v>21.77654304</v>
       </c>
       <c r="O17">
-        <v>3.277951365</v>
+        <v>3.266481456</v>
       </c>
       <c r="P17">
-        <v>18.575057735</v>
+        <v>18.510061584</v>
       </c>
       <c r="Q17">
-        <v>28.175057735</v>
+        <v>28.110061584</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08757167957502851</v>
+        <v>0.08800409861824826</v>
       </c>
       <c r="T17">
-        <v>0.7650629810245845</v>
+        <v>0.7729828876604499</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.05246946597397</v>
+        <v>18.79919012435059</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08076424283932854</v>
+        <v>0.08067930803988285</v>
       </c>
       <c r="C18">
-        <v>133.1043905953758</v>
+        <v>131.9375916085828</v>
       </c>
       <c r="D18">
-        <v>145.1275905953758</v>
+        <v>145.4809916085828</v>
       </c>
       <c r="E18">
-        <v>15.1032</v>
+        <v>16.6234</v>
       </c>
       <c r="F18">
-        <v>24.3232</v>
+        <v>25.8434</v>
       </c>
       <c r="G18">
         <v>12.3</v>
@@ -2763,28 +2763,28 @@
         <v>23</v>
       </c>
       <c r="M18">
-        <v>1.22345696</v>
+        <v>1.29992302</v>
       </c>
       <c r="N18">
-        <v>21.77654304</v>
+        <v>21.70007698</v>
       </c>
       <c r="O18">
-        <v>3.266481456</v>
+        <v>3.255011547</v>
       </c>
       <c r="P18">
-        <v>18.510061584</v>
+        <v>18.445065433</v>
       </c>
       <c r="Q18">
-        <v>28.110061584</v>
+        <v>28.045065433</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08800409861824826</v>
+        <v>0.08844693739744922</v>
       </c>
       <c r="T18">
-        <v>0.7729828876604499</v>
+        <v>0.7810936354200708</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.79919012435059</v>
+        <v>17.6933554111535</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08067930803988285</v>
+        <v>0.08059437324043715</v>
       </c>
       <c r="C19">
-        <v>131.9375916085828</v>
+        <v>130.7725179607677</v>
       </c>
       <c r="D19">
-        <v>145.4809916085828</v>
+        <v>145.8361179607677</v>
       </c>
       <c r="E19">
-        <v>16.6234</v>
+        <v>18.14360000000001</v>
       </c>
       <c r="F19">
-        <v>25.8434</v>
+        <v>27.36360000000001</v>
       </c>
       <c r="G19">
         <v>12.3</v>
@@ -2845,28 +2845,28 @@
         <v>23</v>
       </c>
       <c r="M19">
-        <v>1.29992302</v>
+        <v>1.37638908</v>
       </c>
       <c r="N19">
-        <v>21.70007698</v>
+        <v>21.62361092</v>
       </c>
       <c r="O19">
-        <v>3.255011547</v>
+        <v>3.243541638</v>
       </c>
       <c r="P19">
-        <v>18.445065433</v>
+        <v>18.380069282</v>
       </c>
       <c r="Q19">
-        <v>28.045065433</v>
+        <v>27.980069282</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08844693739744922</v>
+        <v>0.08890057712248434</v>
       </c>
       <c r="T19">
-        <v>0.7810936354200708</v>
+        <v>0.7894022062957802</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.6933554111535</v>
+        <v>16.71039122164497</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08059437324043717</v>
+        <v>0.08050943844099148</v>
       </c>
       <c r="C20">
-        <v>130.7725179607676</v>
+        <v>129.6091823177636</v>
       </c>
       <c r="D20">
-        <v>145.8361179607676</v>
+        <v>146.1929823177636</v>
       </c>
       <c r="E20">
-        <v>18.1436</v>
+        <v>19.6638</v>
       </c>
       <c r="F20">
-        <v>27.3636</v>
+        <v>28.8838</v>
       </c>
       <c r="G20">
         <v>12.3</v>
@@ -2927,28 +2927,28 @@
         <v>23</v>
       </c>
       <c r="M20">
-        <v>1.37638908</v>
+        <v>1.45285514</v>
       </c>
       <c r="N20">
-        <v>21.62361092</v>
+        <v>21.54714486</v>
       </c>
       <c r="O20">
-        <v>3.243541638</v>
+        <v>3.232071729</v>
       </c>
       <c r="P20">
-        <v>18.380069282</v>
+        <v>18.315073131</v>
       </c>
       <c r="Q20">
-        <v>27.980069282</v>
+        <v>27.915073131</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08890057712248434</v>
+        <v>0.08936541782838453</v>
       </c>
       <c r="T20">
-        <v>0.7894022062957802</v>
+        <v>0.7979159270696552</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.71039122164497</v>
+        <v>15.83089694682155</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08050943844099148</v>
+        <v>0.0804245036415458</v>
       </c>
       <c r="C21">
-        <v>129.6091823177636</v>
+        <v>128.4475974696824</v>
       </c>
       <c r="D21">
-        <v>146.1929823177636</v>
+        <v>146.5515974696824</v>
       </c>
       <c r="E21">
-        <v>19.6638</v>
+        <v>21.184</v>
       </c>
       <c r="F21">
-        <v>28.8838</v>
+        <v>30.404</v>
       </c>
       <c r="G21">
         <v>12.3</v>
@@ -3009,28 +3009,28 @@
         <v>23</v>
       </c>
       <c r="M21">
-        <v>1.45285514</v>
+        <v>1.5293212</v>
       </c>
       <c r="N21">
-        <v>21.54714486</v>
+        <v>21.4706788</v>
       </c>
       <c r="O21">
-        <v>3.232071729</v>
+        <v>3.22060182</v>
       </c>
       <c r="P21">
-        <v>18.315073131</v>
+        <v>18.25007698</v>
       </c>
       <c r="Q21">
-        <v>27.915073131</v>
+        <v>27.85007698</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08936541782838453</v>
+        <v>0.08984187955193224</v>
       </c>
       <c r="T21">
-        <v>0.7979159270696552</v>
+        <v>0.8066424908628771</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.83089694682155</v>
+        <v>15.03935209948048</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0804245036415458</v>
+        <v>0.0803395688421001</v>
       </c>
       <c r="C22">
-        <v>128.4475974696824</v>
+        <v>127.2877763324423</v>
       </c>
       <c r="D22">
-        <v>146.5515974696824</v>
+        <v>146.9119763324423</v>
       </c>
       <c r="E22">
-        <v>21.184</v>
+        <v>22.70420000000001</v>
       </c>
       <c r="F22">
-        <v>30.404</v>
+        <v>31.92420000000001</v>
       </c>
       <c r="G22">
         <v>12.3</v>
@@ -3091,28 +3091,28 @@
         <v>23</v>
       </c>
       <c r="M22">
-        <v>1.5293212</v>
+        <v>1.60578726</v>
       </c>
       <c r="N22">
-        <v>21.4706788</v>
+        <v>21.39421274</v>
       </c>
       <c r="O22">
-        <v>3.22060182</v>
+        <v>3.209131911</v>
       </c>
       <c r="P22">
-        <v>18.25007698</v>
+        <v>18.185080829</v>
       </c>
       <c r="Q22">
-        <v>27.85007698</v>
+        <v>27.785080829</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08984187955193224</v>
+        <v>0.09033040359759506</v>
       </c>
       <c r="T22">
-        <v>0.8066424908628771</v>
+        <v>0.8155899803217503</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.03935209948048</v>
+        <v>14.32319247569569</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0803395688421001</v>
+        <v>0.08025463404265441</v>
       </c>
       <c r="C23">
-        <v>127.2877763324423</v>
+        <v>126.1297319493186</v>
       </c>
       <c r="D23">
-        <v>146.9119763324423</v>
+        <v>147.2741319493186</v>
       </c>
       <c r="E23">
-        <v>22.7042</v>
+        <v>24.2244</v>
       </c>
       <c r="F23">
-        <v>31.9242</v>
+        <v>33.4444</v>
       </c>
       <c r="G23">
         <v>12.3</v>
@@ -3173,28 +3173,28 @@
         <v>23</v>
       </c>
       <c r="M23">
-        <v>1.60578726</v>
+        <v>1.68225332</v>
       </c>
       <c r="N23">
-        <v>21.39421274</v>
+        <v>21.31774668</v>
       </c>
       <c r="O23">
-        <v>3.209131911</v>
+        <v>3.197662002</v>
       </c>
       <c r="P23">
-        <v>18.185080829</v>
+        <v>18.120084678</v>
       </c>
       <c r="Q23">
-        <v>27.785080829</v>
+        <v>27.720084678</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09033040359759506</v>
+        <v>0.09083145390083899</v>
       </c>
       <c r="T23">
-        <v>0.8155899803217502</v>
+        <v>0.8247668925872612</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.32319247569569</v>
+        <v>13.67213827225498</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08025463404265441</v>
+        <v>0.08016969924320873</v>
       </c>
       <c r="C24">
-        <v>126.1297319493186</v>
+        <v>124.9734774925175</v>
       </c>
       <c r="D24">
-        <v>147.2741319493186</v>
+        <v>147.6380774925175</v>
       </c>
       <c r="E24">
-        <v>24.2244</v>
+        <v>25.74460000000001</v>
       </c>
       <c r="F24">
-        <v>33.4444</v>
+        <v>34.9646</v>
       </c>
       <c r="G24">
         <v>12.3</v>
@@ -3255,28 +3255,28 @@
         <v>23</v>
       </c>
       <c r="M24">
-        <v>1.68225332</v>
+        <v>1.75871938</v>
       </c>
       <c r="N24">
-        <v>21.31774668</v>
+        <v>21.24128062</v>
       </c>
       <c r="O24">
-        <v>3.197662002</v>
+        <v>3.186192093</v>
       </c>
       <c r="P24">
-        <v>18.120084678</v>
+        <v>18.055088527</v>
       </c>
       <c r="Q24">
-        <v>27.720084678</v>
+        <v>27.655088527</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09083145390083899</v>
+        <v>0.09134551849767367</v>
       </c>
       <c r="T24">
-        <v>0.8247668925872612</v>
+        <v>0.8341821662103177</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.67213827225498</v>
+        <v>13.07769747780911</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08016969924320873</v>
+        <v>0.08039076444376303</v>
       </c>
       <c r="C25">
-        <v>124.9734774925175</v>
+        <v>122.5097412123814</v>
       </c>
       <c r="D25">
-        <v>147.6380774925175</v>
+        <v>146.6945412123814</v>
       </c>
       <c r="E25">
-        <v>25.74460000000001</v>
+        <v>27.26480000000001</v>
       </c>
       <c r="F25">
-        <v>34.9646</v>
+        <v>36.48480000000001</v>
       </c>
       <c r="G25">
         <v>12.3</v>
@@ -3337,45 +3337,45 @@
         <v>23</v>
       </c>
       <c r="M25">
-        <v>1.75871938</v>
+        <v>1.88991264</v>
       </c>
       <c r="N25">
-        <v>21.24128062</v>
+        <v>21.11008736</v>
       </c>
       <c r="O25">
-        <v>3.186192093</v>
+        <v>3.166513104</v>
       </c>
       <c r="P25">
-        <v>18.055088527</v>
+        <v>17.943574256</v>
       </c>
       <c r="Q25">
-        <v>27.655088527</v>
+        <v>27.543574256</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09134551849767367</v>
+        <v>0.09187311111021451</v>
       </c>
       <c r="T25">
-        <v>0.8341821662103177</v>
+        <v>0.8438452101918757</v>
       </c>
       <c r="U25">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>13.07769747780911</v>
+        <v>12.16987468796441</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08039076444376303</v>
+        <v>0.08031857964431734</v>
       </c>
       <c r="C26">
-        <v>122.5097412123814</v>
+        <v>121.296306906286</v>
       </c>
       <c r="D26">
-        <v>146.6945412123814</v>
+        <v>147.001306906286</v>
       </c>
       <c r="E26">
-        <v>27.2648</v>
+        <v>28.785</v>
       </c>
       <c r="F26">
-        <v>36.4848</v>
+        <v>38.005</v>
       </c>
       <c r="G26">
         <v>12.3</v>
@@ -3419,28 +3419,28 @@
         <v>23</v>
       </c>
       <c r="M26">
-        <v>1.88991264</v>
+        <v>1.968659</v>
       </c>
       <c r="N26">
-        <v>21.11008736</v>
+        <v>21.031341</v>
       </c>
       <c r="O26">
-        <v>3.166513104</v>
+        <v>3.15470115</v>
       </c>
       <c r="P26">
-        <v>17.943574256</v>
+        <v>17.87663985</v>
       </c>
       <c r="Q26">
-        <v>27.543574256</v>
+        <v>27.47663985</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09187311111021451</v>
+        <v>0.09241477285908978</v>
       </c>
       <c r="T26">
-        <v>0.8438452101918757</v>
+        <v>0.8537659353462754</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>12.16987468796441</v>
+        <v>11.68307970044584</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08031857964431734</v>
+        <v>0.08024639484487164</v>
       </c>
       <c r="C27">
-        <v>121.296306906286</v>
+        <v>120.0841582975876</v>
       </c>
       <c r="D27">
-        <v>147.001306906286</v>
+        <v>147.3093582975876</v>
       </c>
       <c r="E27">
-        <v>28.785</v>
+        <v>30.30520000000001</v>
       </c>
       <c r="F27">
-        <v>38.005</v>
+        <v>39.52520000000001</v>
       </c>
       <c r="G27">
         <v>12.3</v>
@@ -3501,28 +3501,28 @@
         <v>23</v>
       </c>
       <c r="M27">
-        <v>1.968659</v>
+        <v>2.04740536</v>
       </c>
       <c r="N27">
-        <v>21.031341</v>
+        <v>20.95259464</v>
       </c>
       <c r="O27">
-        <v>3.15470115</v>
+        <v>3.142889196</v>
       </c>
       <c r="P27">
-        <v>17.87663985</v>
+        <v>17.809705444</v>
       </c>
       <c r="Q27">
-        <v>27.47663985</v>
+        <v>27.409705444</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09241477285908978</v>
+        <v>0.09297107411469141</v>
       </c>
       <c r="T27">
-        <v>0.8537659353462754</v>
+        <v>0.8639547882075508</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.68307970044584</v>
+        <v>11.23373048119792</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08024639484487164</v>
+        <v>0.08017421004542596</v>
       </c>
       <c r="C28">
-        <v>120.0841582975876</v>
+        <v>118.8733034860626</v>
       </c>
       <c r="D28">
-        <v>147.3093582975876</v>
+        <v>147.6187034860626</v>
       </c>
       <c r="E28">
-        <v>30.30520000000001</v>
+        <v>31.82540000000001</v>
       </c>
       <c r="F28">
-        <v>39.52520000000001</v>
+        <v>41.04540000000001</v>
       </c>
       <c r="G28">
         <v>12.3</v>
@@ -3583,28 +3583,28 @@
         <v>23</v>
       </c>
       <c r="M28">
-        <v>2.04740536</v>
+        <v>2.12615172</v>
       </c>
       <c r="N28">
-        <v>20.95259464</v>
+        <v>20.87384828</v>
       </c>
       <c r="O28">
-        <v>3.142889196</v>
+        <v>3.131077242</v>
       </c>
       <c r="P28">
-        <v>17.809705444</v>
+        <v>17.742771038</v>
       </c>
       <c r="Q28">
-        <v>27.409705444</v>
+        <v>27.342771038</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09297107411469141</v>
+        <v>0.09354261650058351</v>
       </c>
       <c r="T28">
-        <v>0.8639547882075508</v>
+        <v>0.8744227877225598</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.23373048119792</v>
+        <v>10.8176663893017</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08017421004542596</v>
+        <v>0.08010202524598029</v>
       </c>
       <c r="C29">
-        <v>118.8733034860626</v>
+        <v>117.6637506396683</v>
       </c>
       <c r="D29">
-        <v>147.6187034860626</v>
+        <v>147.9293506396683</v>
       </c>
       <c r="E29">
-        <v>31.82540000000001</v>
+        <v>33.3456</v>
       </c>
       <c r="F29">
-        <v>41.04540000000001</v>
+        <v>42.5656</v>
       </c>
       <c r="G29">
         <v>12.3</v>
@@ -3665,28 +3665,28 @@
         <v>23</v>
       </c>
       <c r="M29">
-        <v>2.12615172</v>
+        <v>2.20489808</v>
       </c>
       <c r="N29">
-        <v>20.87384828</v>
+        <v>20.79510192</v>
       </c>
       <c r="O29">
-        <v>3.131077242</v>
+        <v>3.119265288</v>
       </c>
       <c r="P29">
-        <v>17.742771038</v>
+        <v>17.675836632</v>
       </c>
       <c r="Q29">
-        <v>27.342771038</v>
+        <v>27.275836632</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09354261650058351</v>
+        <v>0.0941300350638615</v>
       </c>
       <c r="T29">
-        <v>0.8744227877225598</v>
+        <v>0.8851815650018745</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.8176663893017</v>
+        <v>10.43132116111235</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08010202524598029</v>
+        <v>0.08002984044653458</v>
       </c>
       <c r="C30">
-        <v>117.6637506396683</v>
+        <v>116.4555079952609</v>
       </c>
       <c r="D30">
-        <v>147.9293506396683</v>
+        <v>148.2413079952609</v>
       </c>
       <c r="E30">
-        <v>33.3456</v>
+        <v>34.86580000000001</v>
       </c>
       <c r="F30">
-        <v>42.5656</v>
+        <v>44.08580000000001</v>
       </c>
       <c r="G30">
         <v>12.3</v>
@@ -3747,28 +3747,28 @@
         <v>23</v>
       </c>
       <c r="M30">
-        <v>2.20489808</v>
+        <v>2.28364444</v>
       </c>
       <c r="N30">
-        <v>20.79510192</v>
+        <v>20.71635556</v>
       </c>
       <c r="O30">
-        <v>3.119265288</v>
+        <v>3.107453334</v>
       </c>
       <c r="P30">
-        <v>17.675836632</v>
+        <v>17.608902226</v>
       </c>
       <c r="Q30">
-        <v>27.275836632</v>
+        <v>27.208902226</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0941300350638615</v>
+        <v>0.09473400062892195</v>
       </c>
       <c r="T30">
-        <v>0.8851815650018745</v>
+        <v>0.8962434064299022</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.43132116111235</v>
+        <v>10.07162043141882</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08002984044653458</v>
+        <v>0.08039115564708889</v>
       </c>
       <c r="C31">
-        <v>116.4555079952609</v>
+        <v>113.3868821931513</v>
       </c>
       <c r="D31">
-        <v>148.2413079952609</v>
+        <v>146.6928821931513</v>
       </c>
       <c r="E31">
-        <v>34.8658</v>
+        <v>36.386</v>
       </c>
       <c r="F31">
-        <v>44.0858</v>
+        <v>45.606</v>
       </c>
       <c r="G31">
         <v>12.3</v>
@@ -3829,45 +3829,45 @@
         <v>23</v>
       </c>
       <c r="M31">
-        <v>2.28364444</v>
+        <v>2.439921</v>
       </c>
       <c r="N31">
-        <v>20.71635556</v>
+        <v>20.560079</v>
       </c>
       <c r="O31">
-        <v>3.107453334</v>
+        <v>3.08401185</v>
       </c>
       <c r="P31">
-        <v>17.608902226</v>
+        <v>17.47606715</v>
       </c>
       <c r="Q31">
-        <v>27.208902226</v>
+        <v>27.07606715</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09473400062892195</v>
+        <v>0.09535522235298413</v>
       </c>
       <c r="T31">
-        <v>0.8962434064299022</v>
+        <v>0.9076213004701593</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>10.07162043141883</v>
+        <v>9.426534711574678</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08039115564708889</v>
+        <v>0.08033342084764319</v>
       </c>
       <c r="C32">
-        <v>113.3868821931513</v>
+        <v>112.1119311121883</v>
       </c>
       <c r="D32">
-        <v>146.6928821931513</v>
+        <v>146.9381311121883</v>
       </c>
       <c r="E32">
-        <v>36.386</v>
+        <v>37.90620000000001</v>
       </c>
       <c r="F32">
-        <v>45.606</v>
+        <v>47.1262</v>
       </c>
       <c r="G32">
         <v>12.3</v>
@@ -3911,28 +3911,28 @@
         <v>23</v>
       </c>
       <c r="M32">
-        <v>2.439921</v>
+        <v>2.5212517</v>
       </c>
       <c r="N32">
-        <v>20.560079</v>
+        <v>20.4787483</v>
       </c>
       <c r="O32">
-        <v>3.08401185</v>
+        <v>3.071812245</v>
       </c>
       <c r="P32">
-        <v>17.47606715</v>
+        <v>17.406936055</v>
       </c>
       <c r="Q32">
-        <v>27.07606715</v>
+        <v>27.006936055</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09535522235298413</v>
+        <v>0.09599445050383074</v>
       </c>
       <c r="T32">
-        <v>0.9076213004701593</v>
+        <v>0.9193289885405689</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.426534711574678</v>
+        <v>9.122452946685172</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08033342084764319</v>
+        <v>0.08027568604819751</v>
       </c>
       <c r="C33">
-        <v>112.1119311121883</v>
+        <v>110.8378014447358</v>
       </c>
       <c r="D33">
-        <v>146.9381311121883</v>
+        <v>147.1842014447358</v>
       </c>
       <c r="E33">
-        <v>37.90620000000001</v>
+        <v>39.42640000000001</v>
       </c>
       <c r="F33">
-        <v>47.1262</v>
+        <v>48.64640000000001</v>
       </c>
       <c r="G33">
         <v>12.3</v>
@@ -3993,28 +3993,28 @@
         <v>23</v>
       </c>
       <c r="M33">
-        <v>2.5212517</v>
+        <v>2.6025824</v>
       </c>
       <c r="N33">
-        <v>20.4787483</v>
+        <v>20.3974176</v>
       </c>
       <c r="O33">
-        <v>3.071812245</v>
+        <v>3.05961264</v>
       </c>
       <c r="P33">
-        <v>17.406936055</v>
+        <v>17.33780496</v>
       </c>
       <c r="Q33">
-        <v>27.006936055</v>
+        <v>26.93780496</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09599445050383074</v>
+        <v>0.09665247948264341</v>
       </c>
       <c r="T33">
-        <v>0.9193289885405689</v>
+        <v>0.9313810203777551</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.122452946685172</v>
+        <v>8.837376292101261</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08027568604819751</v>
+        <v>0.08021795124875182</v>
       </c>
       <c r="C34">
-        <v>110.8378014447358</v>
+        <v>109.5644973244635</v>
       </c>
       <c r="D34">
-        <v>147.1842014447358</v>
+        <v>147.4310973244635</v>
       </c>
       <c r="E34">
-        <v>39.42640000000001</v>
+        <v>40.9466</v>
       </c>
       <c r="F34">
-        <v>48.64640000000001</v>
+        <v>50.1666</v>
       </c>
       <c r="G34">
         <v>12.3</v>
@@ -4075,28 +4075,28 @@
         <v>23</v>
       </c>
       <c r="M34">
-        <v>2.6025824</v>
+        <v>2.6839131</v>
       </c>
       <c r="N34">
-        <v>20.3974176</v>
+        <v>20.3160869</v>
       </c>
       <c r="O34">
-        <v>3.05961264</v>
+        <v>3.047413034999999</v>
       </c>
       <c r="P34">
-        <v>17.33780496</v>
+        <v>17.268673865</v>
       </c>
       <c r="Q34">
-        <v>26.93780496</v>
+        <v>26.868673865</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09665247948264341</v>
+        <v>0.09733015111754004</v>
       </c>
       <c r="T34">
-        <v>0.9313810203777551</v>
+        <v>0.9437928143593349</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.837376292101261</v>
+        <v>8.569577010522433</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08021795124875182</v>
+        <v>0.08016021644930613</v>
       </c>
       <c r="C35">
-        <v>109.5644973244635</v>
+        <v>108.2920229128237</v>
       </c>
       <c r="D35">
-        <v>147.4310973244635</v>
+        <v>147.6788229128237</v>
       </c>
       <c r="E35">
-        <v>40.9466</v>
+        <v>42.46680000000001</v>
       </c>
       <c r="F35">
-        <v>50.1666</v>
+        <v>51.68680000000001</v>
       </c>
       <c r="G35">
         <v>12.3</v>
@@ -4157,28 +4157,28 @@
         <v>23</v>
       </c>
       <c r="M35">
-        <v>2.6839131</v>
+        <v>2.7652438</v>
       </c>
       <c r="N35">
-        <v>20.3160869</v>
+        <v>20.2347562</v>
       </c>
       <c r="O35">
-        <v>3.047413034999999</v>
+        <v>3.03521343</v>
       </c>
       <c r="P35">
-        <v>17.268673865</v>
+        <v>17.19954277</v>
       </c>
       <c r="Q35">
-        <v>26.868673865</v>
+        <v>26.79954277</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09733015111754004</v>
+        <v>0.09802835825652445</v>
       </c>
       <c r="T35">
-        <v>0.9437928143593349</v>
+        <v>0.9565807233100537</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.569577010522433</v>
+        <v>8.317530627860009</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08016021644930613</v>
+        <v>0.08010248164986045</v>
       </c>
       <c r="C36">
-        <v>108.2920229128237</v>
+        <v>107.0203823992853</v>
       </c>
       <c r="D36">
-        <v>147.6788229128237</v>
+        <v>147.9273823992852</v>
       </c>
       <c r="E36">
-        <v>42.46680000000001</v>
+        <v>43.98700000000001</v>
       </c>
       <c r="F36">
-        <v>51.68680000000001</v>
+        <v>53.20700000000001</v>
       </c>
       <c r="G36">
         <v>12.3</v>
@@ -4239,28 +4239,28 @@
         <v>23</v>
       </c>
       <c r="M36">
-        <v>2.7652438</v>
+        <v>2.8465745</v>
       </c>
       <c r="N36">
-        <v>20.2347562</v>
+        <v>20.1534255</v>
       </c>
       <c r="O36">
-        <v>3.03521343</v>
+        <v>3.023013825</v>
       </c>
       <c r="P36">
-        <v>17.19954277</v>
+        <v>17.130411675</v>
       </c>
       <c r="Q36">
-        <v>26.79954277</v>
+        <v>26.730411675</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09802835825652445</v>
+        <v>0.098748048692093</v>
       </c>
       <c r="T36">
-        <v>0.9565807233100537</v>
+        <v>0.969762106382333</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.317530627860009</v>
+        <v>8.079886895635438</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08010248164986045</v>
+        <v>0.08004474685041474</v>
       </c>
       <c r="C37">
-        <v>107.0203823992853</v>
+        <v>105.7495800015703</v>
       </c>
       <c r="D37">
-        <v>147.9273823992852</v>
+        <v>148.1767800015703</v>
       </c>
       <c r="E37">
-        <v>43.98700000000001</v>
+        <v>45.50720000000001</v>
       </c>
       <c r="F37">
-        <v>53.20700000000001</v>
+        <v>54.72720000000001</v>
       </c>
       <c r="G37">
         <v>12.3</v>
@@ -4321,28 +4321,28 @@
         <v>23</v>
       </c>
       <c r="M37">
-        <v>2.8465745</v>
+        <v>2.927905200000001</v>
       </c>
       <c r="N37">
-        <v>20.1534255</v>
+        <v>20.0720948</v>
       </c>
       <c r="O37">
-        <v>3.023013825</v>
+        <v>3.01081422</v>
       </c>
       <c r="P37">
-        <v>17.130411675</v>
+        <v>17.06128058</v>
       </c>
       <c r="Q37">
-        <v>26.730411675</v>
+        <v>26.66128058</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.098748048692093</v>
+        <v>0.09949022945377306</v>
       </c>
       <c r="T37">
-        <v>0.969762106382333</v>
+        <v>0.9833554076756209</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.079886895635438</v>
+        <v>7.855445592978897</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08004474685041475</v>
+        <v>0.07998701205096907</v>
       </c>
       <c r="C38">
-        <v>105.7495800015702</v>
+        <v>104.4796199658919</v>
       </c>
       <c r="D38">
-        <v>148.1767800015702</v>
+        <v>148.4270199658918</v>
       </c>
       <c r="E38">
-        <v>45.5072</v>
+        <v>47.02740000000001</v>
       </c>
       <c r="F38">
-        <v>54.7272</v>
+        <v>56.24740000000001</v>
       </c>
       <c r="G38">
         <v>12.3</v>
@@ -4403,28 +4403,28 @@
         <v>23</v>
       </c>
       <c r="M38">
-        <v>2.9279052</v>
+        <v>3.0092359</v>
       </c>
       <c r="N38">
-        <v>20.0720948</v>
+        <v>19.9907641</v>
       </c>
       <c r="O38">
-        <v>3.01081422</v>
+        <v>2.998614615</v>
       </c>
       <c r="P38">
-        <v>17.06128058</v>
+        <v>16.992149485</v>
       </c>
       <c r="Q38">
-        <v>26.66128058</v>
+        <v>26.592149485</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09949022945377306</v>
+        <v>0.1002559715094747</v>
       </c>
       <c r="T38">
-        <v>0.9833554076756208</v>
+        <v>0.9973802423432989</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.855445592978898</v>
+        <v>7.643136252628117</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07998701205096907</v>
+        <v>0.08018767725152337</v>
       </c>
       <c r="C39">
-        <v>104.4796199658919</v>
+        <v>102.0932917446898</v>
       </c>
       <c r="D39">
-        <v>148.4270199658918</v>
+        <v>147.5608917446897</v>
       </c>
       <c r="E39">
-        <v>47.02740000000001</v>
+        <v>48.5476</v>
       </c>
       <c r="F39">
-        <v>56.24740000000001</v>
+        <v>57.7676</v>
       </c>
       <c r="G39">
         <v>12.3</v>
@@ -4485,45 +4485,45 @@
         <v>23</v>
       </c>
       <c r="M39">
-        <v>3.0092359</v>
+        <v>3.13678068</v>
       </c>
       <c r="N39">
-        <v>19.9907641</v>
+        <v>19.86321932</v>
       </c>
       <c r="O39">
-        <v>2.998614615</v>
+        <v>2.979482898</v>
       </c>
       <c r="P39">
-        <v>16.992149485</v>
+        <v>16.883736422</v>
       </c>
       <c r="Q39">
-        <v>26.592149485</v>
+        <v>26.483736422</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1002559715094747</v>
+        <v>0.1010464149218119</v>
       </c>
       <c r="T39">
-        <v>0.9973802423432989</v>
+        <v>1.011857491032515</v>
       </c>
       <c r="U39">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.15</v>
       </c>
       <c r="W39">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>7.643136252628117</v>
+        <v>7.332358346456022</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08018767725152337</v>
+        <v>0.08013674245207769</v>
       </c>
       <c r="C40">
-        <v>102.0932917446898</v>
+        <v>100.7919821778032</v>
       </c>
       <c r="D40">
-        <v>147.5608917446897</v>
+        <v>147.7797821778032</v>
       </c>
       <c r="E40">
-        <v>48.5476</v>
+        <v>50.06780000000001</v>
       </c>
       <c r="F40">
-        <v>57.7676</v>
+        <v>59.2878</v>
       </c>
       <c r="G40">
         <v>12.3</v>
@@ -4567,28 +4567,28 @@
         <v>23</v>
       </c>
       <c r="M40">
-        <v>3.13678068</v>
+        <v>3.21932754</v>
       </c>
       <c r="N40">
-        <v>19.86321932</v>
+        <v>19.78067246</v>
       </c>
       <c r="O40">
-        <v>2.979482898</v>
+        <v>2.967100869</v>
       </c>
       <c r="P40">
-        <v>16.883736422</v>
+        <v>16.813571591</v>
       </c>
       <c r="Q40">
-        <v>26.483736422</v>
+        <v>26.413571591</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1010464149218119</v>
+        <v>0.1018627745116028</v>
       </c>
       <c r="T40">
-        <v>1.011857491032515</v>
+        <v>1.026809403613181</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.332358346456022</v>
+        <v>7.144349158085356</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08013674245207769</v>
+        <v>0.080085807652632</v>
       </c>
       <c r="C41">
-        <v>100.7919821778032</v>
+        <v>99.49132297566386</v>
       </c>
       <c r="D41">
-        <v>147.7797821778032</v>
+        <v>147.9993229756639</v>
       </c>
       <c r="E41">
-        <v>50.06780000000001</v>
+        <v>51.58800000000001</v>
       </c>
       <c r="F41">
-        <v>59.2878</v>
+        <v>60.80800000000001</v>
       </c>
       <c r="G41">
         <v>12.3</v>
@@ -4649,28 +4649,28 @@
         <v>23</v>
       </c>
       <c r="M41">
-        <v>3.21932754</v>
+        <v>3.3018744</v>
       </c>
       <c r="N41">
-        <v>19.78067246</v>
+        <v>19.6981256</v>
       </c>
       <c r="O41">
-        <v>2.967100869</v>
+        <v>2.95471884</v>
       </c>
       <c r="P41">
-        <v>16.813571591</v>
+        <v>16.74340676</v>
       </c>
       <c r="Q41">
-        <v>26.413571591</v>
+        <v>26.34340676</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1018627745116028</v>
+        <v>0.10270634608772</v>
       </c>
       <c r="T41">
-        <v>1.026809403613181</v>
+        <v>1.042259713279869</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.144349158085356</v>
+        <v>6.965740429133222</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.080085807652632</v>
+        <v>0.08003487285318631</v>
       </c>
       <c r="C42">
-        <v>99.49132297566386</v>
+        <v>98.19131704111845</v>
       </c>
       <c r="D42">
-        <v>147.9993229756639</v>
+        <v>148.2195170411185</v>
       </c>
       <c r="E42">
-        <v>51.58800000000001</v>
+        <v>53.10820000000001</v>
       </c>
       <c r="F42">
-        <v>60.80800000000001</v>
+        <v>62.32820000000001</v>
       </c>
       <c r="G42">
         <v>12.3</v>
@@ -4731,28 +4731,28 @@
         <v>23</v>
       </c>
       <c r="M42">
-        <v>3.3018744</v>
+        <v>3.384421260000001</v>
       </c>
       <c r="N42">
-        <v>19.6981256</v>
+        <v>19.61557874</v>
       </c>
       <c r="O42">
-        <v>2.95471884</v>
+        <v>2.942336811</v>
       </c>
       <c r="P42">
-        <v>16.74340676</v>
+        <v>16.673241929</v>
       </c>
       <c r="Q42">
-        <v>26.34340676</v>
+        <v>26.273241929</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.10270634608772</v>
+        <v>0.1035785133104853</v>
       </c>
       <c r="T42">
-        <v>1.042259713279869</v>
+        <v>1.058233762257292</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.965740429133222</v>
+        <v>6.795844321105581</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08003487285318631</v>
+        <v>0.07998393805374061</v>
       </c>
       <c r="C43">
-        <v>98.19131704111845</v>
+        <v>96.89196729431508</v>
       </c>
       <c r="D43">
-        <v>148.2195170411185</v>
+        <v>148.4403672943151</v>
       </c>
       <c r="E43">
-        <v>53.10820000000001</v>
+        <v>54.62840000000001</v>
       </c>
       <c r="F43">
-        <v>62.32820000000001</v>
+        <v>63.84840000000001</v>
       </c>
       <c r="G43">
         <v>12.3</v>
@@ -4813,28 +4813,28 @@
         <v>23</v>
       </c>
       <c r="M43">
-        <v>3.384421260000001</v>
+        <v>3.466968120000001</v>
       </c>
       <c r="N43">
-        <v>19.61557874</v>
+        <v>19.53303188</v>
       </c>
       <c r="O43">
-        <v>2.942336811</v>
+        <v>2.929954782</v>
       </c>
       <c r="P43">
-        <v>16.673241929</v>
+        <v>16.603077098</v>
       </c>
       <c r="Q43">
-        <v>26.273241929</v>
+        <v>26.203077098</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1035785133104853</v>
+        <v>0.10448075526507</v>
       </c>
       <c r="T43">
-        <v>1.058233762257292</v>
+        <v>1.074758640509799</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.795844321105581</v>
+        <v>6.6340385039364</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07998393805374063</v>
+        <v>0.07993300325429493</v>
       </c>
       <c r="C44">
-        <v>96.89196729431504</v>
+        <v>95.59327667283212</v>
       </c>
       <c r="D44">
-        <v>148.440367294315</v>
+        <v>148.6618766728321</v>
       </c>
       <c r="E44">
-        <v>54.62840000000001</v>
+        <v>56.1486</v>
       </c>
       <c r="F44">
-        <v>63.84840000000001</v>
+        <v>65.3686</v>
       </c>
       <c r="G44">
         <v>12.3</v>
@@ -4895,28 +4895,28 @@
         <v>23</v>
       </c>
       <c r="M44">
-        <v>3.46696812</v>
+        <v>3.54951498</v>
       </c>
       <c r="N44">
-        <v>19.53303188</v>
+        <v>19.45048502</v>
       </c>
       <c r="O44">
-        <v>2.929954782</v>
+        <v>2.917572753</v>
       </c>
       <c r="P44">
-        <v>16.603077098</v>
+        <v>16.532912267</v>
       </c>
       <c r="Q44">
-        <v>26.203077098</v>
+        <v>26.132912267</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.10448075526507</v>
+        <v>0.1054146548320964</v>
       </c>
       <c r="T44">
-        <v>1.074758640509799</v>
+        <v>1.091863339051867</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.634038503936401</v>
+        <v>6.479758538728578</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07993300325429493</v>
+        <v>0.07988206845484924</v>
       </c>
       <c r="C45">
-        <v>95.59327667283212</v>
+        <v>94.29524813180865</v>
       </c>
       <c r="D45">
-        <v>148.6618766728321</v>
+        <v>148.8840481318086</v>
       </c>
       <c r="E45">
-        <v>56.1486</v>
+        <v>57.6688</v>
       </c>
       <c r="F45">
-        <v>65.3686</v>
+        <v>66.8888</v>
       </c>
       <c r="G45">
         <v>12.3</v>
@@ -4977,28 +4977,28 @@
         <v>23</v>
       </c>
       <c r="M45">
-        <v>3.54951498</v>
+        <v>3.63206184</v>
       </c>
       <c r="N45">
-        <v>19.45048502</v>
+        <v>19.36793816</v>
       </c>
       <c r="O45">
-        <v>2.917572753</v>
+        <v>2.905190724</v>
       </c>
       <c r="P45">
-        <v>16.532912267</v>
+        <v>16.462747436</v>
       </c>
       <c r="Q45">
-        <v>26.132912267</v>
+        <v>26.062747436</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1054146548320964</v>
+        <v>0.1063819079550879</v>
       </c>
       <c r="T45">
-        <v>1.091863339051867</v>
+        <v>1.109578919684723</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.479758538728578</v>
+        <v>6.33249129921202</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07988206845484924</v>
+        <v>0.07983113365540356</v>
       </c>
       <c r="C46">
-        <v>94.29524813180865</v>
+        <v>92.9978846440754</v>
       </c>
       <c r="D46">
-        <v>148.8840481318086</v>
+        <v>149.1068846440754</v>
       </c>
       <c r="E46">
-        <v>57.6688</v>
+        <v>59.18900000000001</v>
       </c>
       <c r="F46">
-        <v>66.8888</v>
+        <v>68.40900000000001</v>
       </c>
       <c r="G46">
         <v>12.3</v>
@@ -5059,28 +5059,28 @@
         <v>23</v>
       </c>
       <c r="M46">
-        <v>3.63206184</v>
+        <v>3.7146087</v>
       </c>
       <c r="N46">
-        <v>19.36793816</v>
+        <v>19.2853913</v>
       </c>
       <c r="O46">
-        <v>2.905190724</v>
+        <v>2.892808695</v>
       </c>
       <c r="P46">
-        <v>16.462747436</v>
+        <v>16.392582605</v>
       </c>
       <c r="Q46">
-        <v>26.062747436</v>
+        <v>25.992582605</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1063819079550879</v>
+        <v>0.1073843339189156</v>
       </c>
       <c r="T46">
-        <v>1.109578919684723</v>
+        <v>1.127938703249684</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.33249129921202</v>
+        <v>6.191769270340641</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07983113365540356</v>
+        <v>0.08017119885595786</v>
       </c>
       <c r="C47">
-        <v>92.9978846440754</v>
+        <v>90.00243605460921</v>
       </c>
       <c r="D47">
-        <v>149.1068846440754</v>
+        <v>147.6316360546092</v>
       </c>
       <c r="E47">
-        <v>59.18900000000001</v>
+        <v>60.70920000000001</v>
       </c>
       <c r="F47">
-        <v>68.40900000000001</v>
+        <v>69.92920000000001</v>
       </c>
       <c r="G47">
         <v>12.3</v>
@@ -5141,45 +5141,45 @@
         <v>23</v>
       </c>
       <c r="M47">
-        <v>3.7146087</v>
+        <v>3.86708476</v>
       </c>
       <c r="N47">
-        <v>19.2853913</v>
+        <v>19.13291524</v>
       </c>
       <c r="O47">
-        <v>2.892808695</v>
+        <v>2.869937286</v>
       </c>
       <c r="P47">
-        <v>16.392582605</v>
+        <v>16.262977954</v>
       </c>
       <c r="Q47">
-        <v>25.992582605</v>
+        <v>25.862977954</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1073843339189156</v>
+        <v>0.1084238867702923</v>
       </c>
       <c r="T47">
-        <v>1.127938703249684</v>
+        <v>1.146978478798532</v>
       </c>
       <c r="U47">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V47">
         <v>0.15</v>
       </c>
       <c r="W47">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>6.191769270340641</v>
+        <v>5.9476327588951</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08017119885595786</v>
+        <v>0.08012876405651218</v>
       </c>
       <c r="C48">
-        <v>90.00243605460921</v>
+        <v>88.66472788150698</v>
       </c>
       <c r="D48">
-        <v>147.6316360546092</v>
+        <v>147.814127881507</v>
       </c>
       <c r="E48">
-        <v>60.70920000000001</v>
+        <v>62.22940000000001</v>
       </c>
       <c r="F48">
-        <v>69.92920000000001</v>
+        <v>71.44940000000001</v>
       </c>
       <c r="G48">
         <v>12.3</v>
@@ -5223,28 +5223,28 @@
         <v>23</v>
       </c>
       <c r="M48">
-        <v>3.86708476</v>
+        <v>3.951151820000001</v>
       </c>
       <c r="N48">
-        <v>19.13291524</v>
+        <v>19.04884818</v>
       </c>
       <c r="O48">
-        <v>2.869937286</v>
+        <v>2.857327227</v>
       </c>
       <c r="P48">
-        <v>16.262977954</v>
+        <v>16.191520953</v>
       </c>
       <c r="Q48">
-        <v>25.862977954</v>
+        <v>25.791520953</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1084238867702923</v>
+        <v>0.109502668031155</v>
       </c>
       <c r="T48">
-        <v>1.146978478798532</v>
+        <v>1.166736736443562</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.9476327588951</v>
+        <v>5.821087381046269</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08012876405651218</v>
+        <v>0.08008632925706649</v>
       </c>
       <c r="C49">
-        <v>88.66472788150698</v>
+        <v>87.32747143387334</v>
       </c>
       <c r="D49">
-        <v>147.814127881507</v>
+        <v>147.9970714338733</v>
       </c>
       <c r="E49">
-        <v>62.22940000000001</v>
+        <v>63.74960000000002</v>
       </c>
       <c r="F49">
-        <v>71.44940000000001</v>
+        <v>72.96960000000001</v>
       </c>
       <c r="G49">
         <v>12.3</v>
@@ -5305,28 +5305,28 @@
         <v>23</v>
       </c>
       <c r="M49">
-        <v>3.951151820000001</v>
+        <v>4.035218880000001</v>
       </c>
       <c r="N49">
-        <v>19.04884818</v>
+        <v>18.96478112</v>
       </c>
       <c r="O49">
-        <v>2.857327227</v>
+        <v>2.844717167999999</v>
       </c>
       <c r="P49">
-        <v>16.191520953</v>
+        <v>16.120063952</v>
       </c>
       <c r="Q49">
-        <v>25.791520953</v>
+        <v>25.720063952</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.109502668031155</v>
+        <v>0.110622940878974</v>
       </c>
       <c r="T49">
-        <v>1.166736736443562</v>
+        <v>1.18725492707494</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.821087381046269</v>
+        <v>5.69981472727447</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08008632925706649</v>
+        <v>0.08004389445762079</v>
       </c>
       <c r="C50">
-        <v>87.32747143387336</v>
+        <v>85.99066839103369</v>
       </c>
       <c r="D50">
-        <v>147.9970714338733</v>
+        <v>148.1804683910337</v>
       </c>
       <c r="E50">
-        <v>63.7496</v>
+        <v>65.2698</v>
       </c>
       <c r="F50">
-        <v>72.9696</v>
+        <v>74.4898</v>
       </c>
       <c r="G50">
         <v>12.3</v>
@@ -5387,28 +5387,28 @@
         <v>23</v>
       </c>
       <c r="M50">
-        <v>4.03521888</v>
+        <v>4.11928594</v>
       </c>
       <c r="N50">
-        <v>18.96478112</v>
+        <v>18.88071406</v>
       </c>
       <c r="O50">
-        <v>2.844717167999999</v>
+        <v>2.832107109</v>
       </c>
       <c r="P50">
-        <v>16.120063952</v>
+        <v>16.048606951</v>
       </c>
       <c r="Q50">
-        <v>25.720063952</v>
+        <v>25.648606951</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.110622940878974</v>
+        <v>0.1117871459953349</v>
       </c>
       <c r="T50">
-        <v>1.18725492707494</v>
+        <v>1.208577752633039</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.699814727274471</v>
+        <v>5.583491977738258</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08004389445762079</v>
+        <v>0.08000145965817511</v>
       </c>
       <c r="C51">
-        <v>85.99066839103369</v>
+        <v>84.65432044064754</v>
       </c>
       <c r="D51">
-        <v>148.1804683910337</v>
+        <v>148.3643204406475</v>
       </c>
       <c r="E51">
-        <v>65.2698</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="F51">
-        <v>74.4898</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="G51">
         <v>12.3</v>
@@ -5469,28 +5469,28 @@
         <v>23</v>
       </c>
       <c r="M51">
-        <v>4.11928594</v>
+        <v>4.203353000000001</v>
       </c>
       <c r="N51">
-        <v>18.88071406</v>
+        <v>18.796647</v>
       </c>
       <c r="O51">
-        <v>2.832107109</v>
+        <v>2.81949705</v>
       </c>
       <c r="P51">
-        <v>16.048606951</v>
+        <v>15.97714995</v>
       </c>
       <c r="Q51">
-        <v>25.648606951</v>
+        <v>25.57714995</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1117871459953349</v>
+        <v>0.1129979193163502</v>
       </c>
       <c r="T51">
-        <v>1.208577752633039</v>
+        <v>1.230753491213462</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.583491977738258</v>
+        <v>5.471822138183493</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08000145965817511</v>
+        <v>0.07995902485872942</v>
       </c>
       <c r="C52">
-        <v>84.65432044064754</v>
+        <v>83.31842927876079</v>
       </c>
       <c r="D52">
-        <v>148.3643204406475</v>
+        <v>148.5486292787608</v>
       </c>
       <c r="E52">
-        <v>66.79000000000001</v>
+        <v>68.31020000000001</v>
       </c>
       <c r="F52">
-        <v>76.01000000000001</v>
+        <v>77.53020000000001</v>
       </c>
       <c r="G52">
         <v>12.3</v>
@@ -5551,28 +5551,28 @@
         <v>23</v>
       </c>
       <c r="M52">
-        <v>4.203353000000001</v>
+        <v>4.287420060000001</v>
       </c>
       <c r="N52">
-        <v>18.796647</v>
+        <v>18.71257994</v>
       </c>
       <c r="O52">
-        <v>2.81949705</v>
+        <v>2.806886990999999</v>
       </c>
       <c r="P52">
-        <v>15.97714995</v>
+        <v>15.905692949</v>
       </c>
       <c r="Q52">
-        <v>25.57714995</v>
+        <v>25.505692949</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1129979193163502</v>
+        <v>0.1142581119565907</v>
       </c>
       <c r="T52">
-        <v>1.230753491213462</v>
+        <v>1.253834361980841</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.471822138183493</v>
+        <v>5.364531508023031</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07995902485872942</v>
+        <v>0.07991659005928373</v>
       </c>
       <c r="C53">
-        <v>83.31842927876079</v>
+        <v>81.98299660985758</v>
       </c>
       <c r="D53">
-        <v>148.5486292787608</v>
+        <v>148.7333966098576</v>
       </c>
       <c r="E53">
-        <v>68.31020000000001</v>
+        <v>69.83040000000001</v>
       </c>
       <c r="F53">
-        <v>77.53020000000001</v>
+        <v>79.05040000000001</v>
       </c>
       <c r="G53">
         <v>12.3</v>
@@ -5633,28 +5633,28 @@
         <v>23</v>
       </c>
       <c r="M53">
-        <v>4.287420060000001</v>
+        <v>4.371487120000001</v>
       </c>
       <c r="N53">
-        <v>18.71257994</v>
+        <v>18.62851288</v>
       </c>
       <c r="O53">
-        <v>2.806886990999999</v>
+        <v>2.794276932</v>
       </c>
       <c r="P53">
-        <v>15.905692949</v>
+        <v>15.834235948</v>
       </c>
       <c r="Q53">
-        <v>25.505692949</v>
+        <v>25.434235948</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1142581119565907</v>
+        <v>0.1155708126235078</v>
       </c>
       <c r="T53">
-        <v>1.253834361980841</v>
+        <v>1.27787693569686</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.364531508023031</v>
+        <v>5.26136744056105</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07991659005928373</v>
+        <v>0.07987415525983804</v>
       </c>
       <c r="C54">
-        <v>81.98299660985758</v>
+        <v>80.64802414691272</v>
       </c>
       <c r="D54">
-        <v>148.7333966098576</v>
+        <v>148.9186241469127</v>
       </c>
       <c r="E54">
-        <v>69.83040000000001</v>
+        <v>71.35060000000001</v>
       </c>
       <c r="F54">
-        <v>79.05040000000001</v>
+        <v>80.57060000000001</v>
       </c>
       <c r="G54">
         <v>12.3</v>
@@ -5715,28 +5715,28 @@
         <v>23</v>
       </c>
       <c r="M54">
-        <v>4.371487120000001</v>
+        <v>4.455554180000001</v>
       </c>
       <c r="N54">
-        <v>18.62851288</v>
+        <v>18.54444582</v>
       </c>
       <c r="O54">
-        <v>2.794276932</v>
+        <v>2.781666873</v>
       </c>
       <c r="P54">
-        <v>15.834235948</v>
+        <v>15.762778947</v>
       </c>
       <c r="Q54">
-        <v>25.434235948</v>
+        <v>25.362778947</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1155708126235078</v>
+        <v>0.1169393728932724</v>
       </c>
       <c r="T54">
-        <v>1.27787693569686</v>
+        <v>1.302942597656115</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.26136744056105</v>
+        <v>5.162096356776879</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07987415525983804</v>
+        <v>0.07983172046039234</v>
       </c>
       <c r="C55">
-        <v>80.64802414691272</v>
+        <v>79.31351361144506</v>
       </c>
       <c r="D55">
-        <v>148.9186241469127</v>
+        <v>149.1043136114451</v>
       </c>
       <c r="E55">
-        <v>71.35060000000001</v>
+        <v>72.87080000000002</v>
       </c>
       <c r="F55">
-        <v>80.57060000000001</v>
+        <v>82.09080000000002</v>
       </c>
       <c r="G55">
         <v>12.3</v>
@@ -5797,28 +5797,28 @@
         <v>23</v>
       </c>
       <c r="M55">
-        <v>4.455554180000001</v>
+        <v>4.539621240000001</v>
       </c>
       <c r="N55">
-        <v>18.54444582</v>
+        <v>18.46037876</v>
       </c>
       <c r="O55">
-        <v>2.781666873</v>
+        <v>2.769056813999999</v>
       </c>
       <c r="P55">
-        <v>15.762778947</v>
+        <v>15.691321946</v>
       </c>
       <c r="Q55">
-        <v>25.362778947</v>
+        <v>25.291321946</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1169393728932724</v>
+        <v>0.1183674357834616</v>
       </c>
       <c r="T55">
-        <v>1.302942597656115</v>
+        <v>1.329098071004902</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.162096356776879</v>
+        <v>5.066501979799529</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07983172046039234</v>
+        <v>0.07978928566094666</v>
       </c>
       <c r="C56">
-        <v>79.31351361144506</v>
+        <v>77.97946673357018</v>
       </c>
       <c r="D56">
-        <v>149.1043136114451</v>
+        <v>149.2904667335702</v>
       </c>
       <c r="E56">
-        <v>72.87080000000002</v>
+        <v>74.39100000000002</v>
       </c>
       <c r="F56">
-        <v>82.09080000000002</v>
+        <v>83.61100000000002</v>
       </c>
       <c r="G56">
         <v>12.3</v>
@@ -5879,28 +5879,28 @@
         <v>23</v>
       </c>
       <c r="M56">
-        <v>4.539621240000001</v>
+        <v>4.623688300000001</v>
       </c>
       <c r="N56">
-        <v>18.46037876</v>
+        <v>18.3763117</v>
       </c>
       <c r="O56">
-        <v>2.769056813999999</v>
+        <v>2.756446755</v>
       </c>
       <c r="P56">
-        <v>15.691321946</v>
+        <v>15.619864945</v>
       </c>
       <c r="Q56">
-        <v>25.291321946</v>
+        <v>25.219864945</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1183674357834616</v>
+        <v>0.119858968135437</v>
       </c>
       <c r="T56">
-        <v>1.329098071004902</v>
+        <v>1.356416009835858</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.066501979799529</v>
+        <v>4.974383761984992</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07978928566094666</v>
+        <v>0.07974685086150096</v>
       </c>
       <c r="C57">
-        <v>77.97946673357018</v>
+        <v>76.64588525205485</v>
       </c>
       <c r="D57">
-        <v>149.2904667335702</v>
+        <v>149.4770852520548</v>
       </c>
       <c r="E57">
-        <v>74.39100000000002</v>
+        <v>75.91120000000001</v>
       </c>
       <c r="F57">
-        <v>83.61100000000002</v>
+        <v>85.13120000000001</v>
       </c>
       <c r="G57">
         <v>12.3</v>
@@ -5961,28 +5961,28 @@
         <v>23</v>
       </c>
       <c r="M57">
-        <v>4.623688300000001</v>
+        <v>4.70775536</v>
       </c>
       <c r="N57">
-        <v>18.3763117</v>
+        <v>18.29224464</v>
       </c>
       <c r="O57">
-        <v>2.756446755</v>
+        <v>2.743836696</v>
       </c>
       <c r="P57">
-        <v>15.619864945</v>
+        <v>15.548407944</v>
       </c>
       <c r="Q57">
-        <v>25.219864945</v>
+        <v>25.148407944</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.119858968135437</v>
+        <v>0.1214182974125022</v>
       </c>
       <c r="T57">
-        <v>1.356416009835858</v>
+        <v>1.384975673159129</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.974383761984992</v>
+        <v>4.885555480520976</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07974685086150096</v>
+        <v>0.07970441606205528</v>
       </c>
       <c r="C58">
-        <v>76.64588525205485</v>
+        <v>75.31277091437055</v>
       </c>
       <c r="D58">
-        <v>149.4770852520548</v>
+        <v>149.6641709143705</v>
       </c>
       <c r="E58">
-        <v>75.91120000000001</v>
+        <v>77.43140000000001</v>
       </c>
       <c r="F58">
-        <v>85.13120000000001</v>
+        <v>86.65140000000001</v>
       </c>
       <c r="G58">
         <v>12.3</v>
@@ -6043,28 +6043,28 @@
         <v>23</v>
       </c>
       <c r="M58">
-        <v>4.70775536</v>
+        <v>4.791822420000001</v>
       </c>
       <c r="N58">
-        <v>18.29224464</v>
+        <v>18.20817758</v>
       </c>
       <c r="O58">
-        <v>2.743836696</v>
+        <v>2.731226636999999</v>
       </c>
       <c r="P58">
-        <v>15.548407944</v>
+        <v>15.476950943</v>
       </c>
       <c r="Q58">
-        <v>25.148407944</v>
+        <v>25.076950943</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1214182974125022</v>
+        <v>0.1230501536326867</v>
       </c>
       <c r="T58">
-        <v>1.384975673159129</v>
+        <v>1.414863692916042</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.885555480520976</v>
+        <v>4.799843980862712</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07970441606205528</v>
+        <v>0.07966198126260959</v>
       </c>
       <c r="C59">
-        <v>75.31277091437055</v>
+        <v>73.98012547674841</v>
       </c>
       <c r="D59">
-        <v>149.6641709143705</v>
+        <v>149.8517254767484</v>
       </c>
       <c r="E59">
-        <v>77.43140000000001</v>
+        <v>78.95160000000001</v>
       </c>
       <c r="F59">
-        <v>86.65140000000001</v>
+        <v>88.17160000000001</v>
       </c>
       <c r="G59">
         <v>12.3</v>
@@ -6125,28 +6125,28 @@
         <v>23</v>
       </c>
       <c r="M59">
-        <v>4.791822420000001</v>
+        <v>4.875889480000001</v>
       </c>
       <c r="N59">
-        <v>18.20817758</v>
+        <v>18.12411052</v>
       </c>
       <c r="O59">
-        <v>2.731226636999999</v>
+        <v>2.718616578</v>
       </c>
       <c r="P59">
-        <v>15.476950943</v>
+        <v>15.405493942</v>
       </c>
       <c r="Q59">
-        <v>25.076950943</v>
+        <v>25.005493942</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1230501536326867</v>
+        <v>0.1247597172919276</v>
       </c>
       <c r="T59">
-        <v>1.414863692916042</v>
+        <v>1.446174951708997</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.799843980862712</v>
+        <v>4.717088050158183</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07966198126260959</v>
+        <v>0.0796195464631639</v>
       </c>
       <c r="C60">
-        <v>73.98012547674843</v>
+        <v>72.64795070423403</v>
       </c>
       <c r="D60">
-        <v>149.8517254767484</v>
+        <v>150.039750704234</v>
       </c>
       <c r="E60">
-        <v>78.9516</v>
+        <v>80.4718</v>
       </c>
       <c r="F60">
-        <v>88.1716</v>
+        <v>89.6918</v>
       </c>
       <c r="G60">
         <v>12.3</v>
@@ -6207,28 +6207,28 @@
         <v>23</v>
       </c>
       <c r="M60">
-        <v>4.87588948</v>
+        <v>4.95995654</v>
       </c>
       <c r="N60">
-        <v>18.12411052</v>
+        <v>18.04004346</v>
       </c>
       <c r="O60">
-        <v>2.718616578</v>
+        <v>2.706006519</v>
       </c>
       <c r="P60">
-        <v>15.405493942</v>
+        <v>15.334036941</v>
       </c>
       <c r="Q60">
-        <v>25.005493942</v>
+        <v>24.934036941</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1247597172919276</v>
+        <v>0.1265526743003997</v>
       </c>
       <c r="T60">
-        <v>1.446174951708997</v>
+        <v>1.479013588979658</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.717088050158184</v>
+        <v>4.637137405240248</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0796195464631639</v>
+        <v>0.0795771116637182</v>
       </c>
       <c r="C61">
-        <v>72.64795070423403</v>
+        <v>71.31624837074283</v>
       </c>
       <c r="D61">
-        <v>150.039750704234</v>
+        <v>150.2282483707428</v>
       </c>
       <c r="E61">
-        <v>80.4718</v>
+        <v>81.992</v>
       </c>
       <c r="F61">
-        <v>89.6918</v>
+        <v>91.212</v>
       </c>
       <c r="G61">
         <v>12.3</v>
@@ -6289,28 +6289,28 @@
         <v>23</v>
       </c>
       <c r="M61">
-        <v>4.95995654</v>
+        <v>5.0440236</v>
       </c>
       <c r="N61">
-        <v>18.04004346</v>
+        <v>17.9559764</v>
       </c>
       <c r="O61">
-        <v>2.706006519</v>
+        <v>2.69339646</v>
       </c>
       <c r="P61">
-        <v>15.334036941</v>
+        <v>15.26257994</v>
       </c>
       <c r="Q61">
-        <v>24.934036941</v>
+        <v>24.86257994</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1265526743003997</v>
+        <v>0.1284352791592955</v>
       </c>
       <c r="T61">
-        <v>1.479013588979658</v>
+        <v>1.513494158113852</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.637137405240248</v>
+        <v>4.559851781819578</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0795771116637182</v>
+        <v>0.08083092686427253</v>
       </c>
       <c r="C62">
-        <v>71.31624837074283</v>
+        <v>64.41912922470695</v>
       </c>
       <c r="D62">
-        <v>150.2282483707428</v>
+        <v>144.8513292247069</v>
       </c>
       <c r="E62">
-        <v>81.992</v>
+        <v>83.51220000000001</v>
       </c>
       <c r="F62">
-        <v>91.212</v>
+        <v>92.73220000000001</v>
       </c>
       <c r="G62">
         <v>12.3</v>
@@ -6371,45 +6371,45 @@
         <v>23</v>
       </c>
       <c r="M62">
-        <v>5.0440236</v>
+        <v>5.359921160000001</v>
       </c>
       <c r="N62">
-        <v>17.9559764</v>
+        <v>17.64007884</v>
       </c>
       <c r="O62">
-        <v>2.69339646</v>
+        <v>2.646011826</v>
       </c>
       <c r="P62">
-        <v>15.26257994</v>
+        <v>14.994067014</v>
       </c>
       <c r="Q62">
-        <v>24.86257994</v>
+        <v>24.594067014</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1284352791592955</v>
+        <v>0.130414427857109</v>
       </c>
       <c r="T62">
-        <v>1.513494158113852</v>
+        <v>1.54974296156262</v>
       </c>
       <c r="U62">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V62">
         <v>0.15</v>
       </c>
       <c r="W62">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>4.559851781819578</v>
+        <v>4.291107893833274</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08083092686427253</v>
+        <v>0.08080974206482683</v>
       </c>
       <c r="C63">
-        <v>64.41912922470695</v>
+        <v>62.98658043771466</v>
       </c>
       <c r="D63">
-        <v>144.8513292247069</v>
+        <v>144.9389804377147</v>
       </c>
       <c r="E63">
-        <v>83.51220000000001</v>
+        <v>85.03240000000001</v>
       </c>
       <c r="F63">
-        <v>92.73220000000001</v>
+        <v>94.25240000000001</v>
       </c>
       <c r="G63">
         <v>12.3</v>
@@ -6453,28 +6453,28 @@
         <v>23</v>
       </c>
       <c r="M63">
-        <v>5.359921160000001</v>
+        <v>5.447788720000001</v>
       </c>
       <c r="N63">
-        <v>17.64007884</v>
+        <v>17.55221128</v>
       </c>
       <c r="O63">
-        <v>2.646011826</v>
+        <v>2.632831691999999</v>
       </c>
       <c r="P63">
-        <v>14.994067014</v>
+        <v>14.919379588</v>
       </c>
       <c r="Q63">
-        <v>24.594067014</v>
+        <v>24.519379588</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.130414427857109</v>
+        <v>0.1324977422758601</v>
       </c>
       <c r="T63">
-        <v>1.54974296156262</v>
+        <v>1.587899596771849</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.291107893833274</v>
+        <v>4.221896476190802</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08080974206482683</v>
+        <v>0.08078855726538114</v>
       </c>
       <c r="C64">
-        <v>62.98658043771466</v>
+        <v>61.5541377924734</v>
       </c>
       <c r="D64">
-        <v>144.9389804377147</v>
+        <v>145.0267377924734</v>
       </c>
       <c r="E64">
-        <v>85.03240000000001</v>
+        <v>86.55260000000001</v>
       </c>
       <c r="F64">
-        <v>94.25240000000001</v>
+        <v>95.77260000000001</v>
       </c>
       <c r="G64">
         <v>12.3</v>
@@ -6535,28 +6535,28 @@
         <v>23</v>
       </c>
       <c r="M64">
-        <v>5.447788720000001</v>
+        <v>5.535656280000001</v>
       </c>
       <c r="N64">
-        <v>17.55221128</v>
+        <v>17.46434372</v>
       </c>
       <c r="O64">
-        <v>2.632831691999999</v>
+        <v>2.619651558</v>
       </c>
       <c r="P64">
-        <v>14.919379588</v>
+        <v>14.844692162</v>
       </c>
       <c r="Q64">
-        <v>24.519379588</v>
+        <v>24.444692162</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1324977422758601</v>
+        <v>0.1346936682848139</v>
       </c>
       <c r="T64">
-        <v>1.587899596771849</v>
+        <v>1.628118752803199</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.221896476190802</v>
+        <v>4.154882246409995</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08078855726538114</v>
+        <v>0.08076737246593545</v>
       </c>
       <c r="C65">
-        <v>61.5541377924734</v>
+        <v>60.12180148189957</v>
       </c>
       <c r="D65">
-        <v>145.0267377924734</v>
+        <v>145.1146014818996</v>
       </c>
       <c r="E65">
-        <v>86.55260000000001</v>
+        <v>88.07280000000002</v>
       </c>
       <c r="F65">
-        <v>95.77260000000001</v>
+        <v>97.29280000000001</v>
       </c>
       <c r="G65">
         <v>12.3</v>
@@ -6617,28 +6617,28 @@
         <v>23</v>
       </c>
       <c r="M65">
-        <v>5.535656280000001</v>
+        <v>5.623523840000002</v>
       </c>
       <c r="N65">
-        <v>17.46434372</v>
+        <v>17.37647616</v>
       </c>
       <c r="O65">
-        <v>2.619651558</v>
+        <v>2.606471424</v>
       </c>
       <c r="P65">
-        <v>14.844692162</v>
+        <v>14.770004736</v>
       </c>
       <c r="Q65">
-        <v>24.444692162</v>
+        <v>24.370004736</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1346936682848139</v>
+        <v>0.137011590183154</v>
       </c>
       <c r="T65">
-        <v>1.628118752803199</v>
+        <v>1.670572306391846</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.154882246409995</v>
+        <v>4.089962211309839</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08076737246593545</v>
+        <v>0.08074618766648976</v>
       </c>
       <c r="C66">
-        <v>60.12180148189957</v>
+        <v>58.68957169937721</v>
       </c>
       <c r="D66">
-        <v>145.1146014818996</v>
+        <v>145.2025716993772</v>
       </c>
       <c r="E66">
-        <v>88.07280000000002</v>
+        <v>89.59300000000002</v>
       </c>
       <c r="F66">
-        <v>97.29280000000001</v>
+        <v>98.81300000000002</v>
       </c>
       <c r="G66">
         <v>12.3</v>
@@ -6699,28 +6699,28 @@
         <v>23</v>
       </c>
       <c r="M66">
-        <v>5.623523840000002</v>
+        <v>5.711391400000001</v>
       </c>
       <c r="N66">
-        <v>17.37647616</v>
+        <v>17.2886086</v>
       </c>
       <c r="O66">
-        <v>2.606471424</v>
+        <v>2.59329129</v>
       </c>
       <c r="P66">
-        <v>14.770004736</v>
+        <v>14.69531731</v>
       </c>
       <c r="Q66">
-        <v>24.370004736</v>
+        <v>24.29531731</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.137011590183154</v>
+        <v>0.1394619647613993</v>
       </c>
       <c r="T66">
-        <v>1.670572306391846</v>
+        <v>1.715451777328416</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.089962211309839</v>
+        <v>4.027039715751226</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08074618766648976</v>
+        <v>0.08268850286704407</v>
       </c>
       <c r="C67">
-        <v>58.68957169937721</v>
+        <v>49.5239228399376</v>
       </c>
       <c r="D67">
-        <v>145.2025716993772</v>
+        <v>137.5571228399376</v>
       </c>
       <c r="E67">
-        <v>89.59300000000002</v>
+        <v>91.11320000000001</v>
       </c>
       <c r="F67">
-        <v>98.81300000000002</v>
+        <v>100.3332</v>
       </c>
       <c r="G67">
         <v>12.3</v>
@@ -6781,45 +6781,45 @@
         <v>23</v>
       </c>
       <c r="M67">
-        <v>5.711391400000001</v>
+        <v>6.15042516</v>
       </c>
       <c r="N67">
-        <v>17.2886086</v>
+        <v>16.84957484</v>
       </c>
       <c r="O67">
-        <v>2.59329129</v>
+        <v>2.527436226</v>
       </c>
       <c r="P67">
-        <v>14.69531731</v>
+        <v>14.322138614</v>
       </c>
       <c r="Q67">
-        <v>24.29531731</v>
+        <v>23.922138614</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1394619647613993</v>
+        <v>0.1420564790207179</v>
       </c>
       <c r="T67">
-        <v>1.715451777328416</v>
+        <v>1.762971217143608</v>
       </c>
       <c r="U67">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V67">
         <v>0.15</v>
       </c>
       <c r="W67">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>4.027039715751226</v>
+        <v>3.739578874901714</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08268850286704407</v>
+        <v>0.08269706806759838</v>
       </c>
       <c r="C68">
-        <v>49.5239228399376</v>
+        <v>47.97179064568736</v>
       </c>
       <c r="D68">
-        <v>137.5571228399376</v>
+        <v>137.5251906456874</v>
       </c>
       <c r="E68">
-        <v>91.11320000000001</v>
+        <v>92.63340000000001</v>
       </c>
       <c r="F68">
-        <v>100.3332</v>
+        <v>101.8534</v>
       </c>
       <c r="G68">
         <v>12.3</v>
@@ -6863,28 +6863,28 @@
         <v>23</v>
       </c>
       <c r="M68">
-        <v>6.15042516</v>
+        <v>6.243613420000001</v>
       </c>
       <c r="N68">
-        <v>16.84957484</v>
+        <v>16.75638658</v>
       </c>
       <c r="O68">
-        <v>2.527436226</v>
+        <v>2.513457986999999</v>
       </c>
       <c r="P68">
-        <v>14.322138614</v>
+        <v>14.242928593</v>
       </c>
       <c r="Q68">
-        <v>23.922138614</v>
+        <v>23.842928593</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1420564790207179</v>
+        <v>0.14480823656848</v>
       </c>
       <c r="T68">
-        <v>1.762971217143608</v>
+        <v>1.813370623008205</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.739578874901714</v>
+        <v>3.683764264828554</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08269706806759838</v>
+        <v>0.0827056332681527</v>
       </c>
       <c r="C69">
-        <v>47.97179064568736</v>
+        <v>46.41967327332875</v>
       </c>
       <c r="D69">
-        <v>137.5251906456874</v>
+        <v>137.4932732733288</v>
       </c>
       <c r="E69">
-        <v>92.63340000000001</v>
+        <v>94.15360000000001</v>
       </c>
       <c r="F69">
-        <v>101.8534</v>
+        <v>103.3736</v>
       </c>
       <c r="G69">
         <v>12.3</v>
@@ -6945,28 +6945,28 @@
         <v>23</v>
       </c>
       <c r="M69">
-        <v>6.243613420000001</v>
+        <v>6.336801680000001</v>
       </c>
       <c r="N69">
-        <v>16.75638658</v>
+        <v>16.66319832</v>
       </c>
       <c r="O69">
-        <v>2.513457986999999</v>
+        <v>2.499479748</v>
       </c>
       <c r="P69">
-        <v>14.242928593</v>
+        <v>14.163718572</v>
       </c>
       <c r="Q69">
-        <v>23.842928593</v>
+        <v>23.763718572</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.14480823656848</v>
+        <v>0.1477319789629772</v>
       </c>
       <c r="T69">
-        <v>1.813370623008205</v>
+        <v>1.86691999173934</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.683764264828554</v>
+        <v>3.629591260934017</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0827056332681527</v>
+        <v>0.08271419846870701</v>
       </c>
       <c r="C70">
-        <v>46.41967327332875</v>
+        <v>44.86757071254435</v>
       </c>
       <c r="D70">
-        <v>137.4932732733288</v>
+        <v>137.4613707125444</v>
       </c>
       <c r="E70">
-        <v>94.15360000000001</v>
+        <v>95.67380000000001</v>
       </c>
       <c r="F70">
-        <v>103.3736</v>
+        <v>104.8938</v>
       </c>
       <c r="G70">
         <v>12.3</v>
@@ -7027,28 +7027,28 @@
         <v>23</v>
       </c>
       <c r="M70">
-        <v>6.336801680000001</v>
+        <v>6.42998994</v>
       </c>
       <c r="N70">
-        <v>16.66319832</v>
+        <v>16.57001006</v>
       </c>
       <c r="O70">
-        <v>2.499479748</v>
+        <v>2.485501509</v>
       </c>
       <c r="P70">
-        <v>14.163718572</v>
+        <v>14.084508551</v>
       </c>
       <c r="Q70">
-        <v>23.763718572</v>
+        <v>23.684508551</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1477319789629772</v>
+        <v>0.1508443498990549</v>
       </c>
       <c r="T70">
-        <v>1.86691999173934</v>
+        <v>1.923924158453128</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.629591260934017</v>
+        <v>3.576988489036423</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08271419846870701</v>
+        <v>0.08272276366926132</v>
       </c>
       <c r="C71">
-        <v>44.86757071254435</v>
+        <v>43.31548295302642</v>
       </c>
       <c r="D71">
-        <v>137.4613707125444</v>
+        <v>137.4294829530264</v>
       </c>
       <c r="E71">
-        <v>95.67380000000001</v>
+        <v>97.19400000000002</v>
       </c>
       <c r="F71">
-        <v>104.8938</v>
+        <v>106.414</v>
       </c>
       <c r="G71">
         <v>12.3</v>
@@ -7109,28 +7109,28 @@
         <v>23</v>
       </c>
       <c r="M71">
-        <v>6.42998994</v>
+        <v>6.523178200000001</v>
       </c>
       <c r="N71">
-        <v>16.57001006</v>
+        <v>16.4768218</v>
       </c>
       <c r="O71">
-        <v>2.485501509</v>
+        <v>2.47152327</v>
       </c>
       <c r="P71">
-        <v>14.084508551</v>
+        <v>14.00529853</v>
       </c>
       <c r="Q71">
-        <v>23.684508551</v>
+        <v>23.60529853</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1508443498990549</v>
+        <v>0.1541642122308711</v>
       </c>
       <c r="T71">
-        <v>1.923924158453128</v>
+        <v>1.984728602947835</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.576988489036423</v>
+        <v>3.525888653478759</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08272276366926132</v>
+        <v>0.08442112886981563</v>
       </c>
       <c r="C72">
-        <v>43.31548295302642</v>
+        <v>35.75181767358423</v>
       </c>
       <c r="D72">
-        <v>137.4294829530264</v>
+        <v>131.3860176735842</v>
       </c>
       <c r="E72">
-        <v>97.19400000000002</v>
+        <v>98.71420000000002</v>
       </c>
       <c r="F72">
-        <v>106.414</v>
+        <v>107.9342</v>
       </c>
       <c r="G72">
         <v>12.3</v>
@@ -7191,45 +7191,45 @@
         <v>23</v>
       </c>
       <c r="M72">
-        <v>6.523178200000001</v>
+        <v>6.918582220000002</v>
       </c>
       <c r="N72">
-        <v>16.4768218</v>
+        <v>16.08141778</v>
       </c>
       <c r="O72">
-        <v>2.47152327</v>
+        <v>2.412212667</v>
       </c>
       <c r="P72">
-        <v>14.00529853</v>
+        <v>13.669205113</v>
       </c>
       <c r="Q72">
-        <v>23.60529853</v>
+        <v>23.269205113</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1541642122308711</v>
+        <v>0.1577130305855712</v>
       </c>
       <c r="T72">
-        <v>1.984728602947835</v>
+        <v>2.049726457407696</v>
       </c>
       <c r="U72">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V72">
         <v>0.15</v>
       </c>
       <c r="W72">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y72">
-        <v>3.525888653478759</v>
+        <v>3.324380526043672</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08442112886981562</v>
+        <v>0.08445349407036994</v>
       </c>
       <c r="C73">
-        <v>35.7518176735843</v>
+        <v>34.12160601967541</v>
       </c>
       <c r="D73">
-        <v>131.3860176735843</v>
+        <v>131.2760060196754</v>
       </c>
       <c r="E73">
-        <v>98.71420000000001</v>
+        <v>100.2344</v>
       </c>
       <c r="F73">
-        <v>107.9342</v>
+        <v>109.4544</v>
       </c>
       <c r="G73">
         <v>12.3</v>
@@ -7273,28 +7273,28 @@
         <v>23</v>
       </c>
       <c r="M73">
-        <v>6.918582220000001</v>
+        <v>7.016027040000001</v>
       </c>
       <c r="N73">
-        <v>16.08141778</v>
+        <v>15.98397296</v>
       </c>
       <c r="O73">
-        <v>2.412212667</v>
+        <v>2.397595944</v>
       </c>
       <c r="P73">
-        <v>13.669205113</v>
+        <v>13.586377016</v>
       </c>
       <c r="Q73">
-        <v>23.269205113</v>
+        <v>23.186377016</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1577130305855711</v>
+        <v>0.1615153359656069</v>
       </c>
       <c r="T73">
-        <v>2.049726457407695</v>
+        <v>2.119367015757545</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.324380526043672</v>
+        <v>3.278208574293066</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08445349407036994</v>
+        <v>0.08448585927092425</v>
       </c>
       <c r="C74">
-        <v>34.12160601967541</v>
+        <v>32.49157844073909</v>
       </c>
       <c r="D74">
-        <v>131.2760060196754</v>
+        <v>131.1661784407391</v>
       </c>
       <c r="E74">
-        <v>100.2344</v>
+        <v>101.7546</v>
       </c>
       <c r="F74">
-        <v>109.4544</v>
+        <v>110.9746</v>
       </c>
       <c r="G74">
         <v>12.3</v>
@@ -7355,28 +7355,28 @@
         <v>23</v>
       </c>
       <c r="M74">
-        <v>7.016027040000001</v>
+        <v>7.113471860000001</v>
       </c>
       <c r="N74">
-        <v>15.98397296</v>
+        <v>15.88652814</v>
       </c>
       <c r="O74">
-        <v>2.397595944</v>
+        <v>2.382979221</v>
       </c>
       <c r="P74">
-        <v>13.586377016</v>
+        <v>13.503548919</v>
       </c>
       <c r="Q74">
-        <v>23.186377016</v>
+        <v>23.103548919</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1615153359656069</v>
+        <v>0.1655992935960157</v>
       </c>
       <c r="T74">
-        <v>2.119367015757545</v>
+        <v>2.194166133985161</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.278208574293066</v>
+        <v>3.233301607521928</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08448585927092425</v>
+        <v>0.08451822447147855</v>
       </c>
       <c r="C75">
-        <v>32.49157844073909</v>
+        <v>30.86173447516153</v>
       </c>
       <c r="D75">
-        <v>131.1661784407391</v>
+        <v>131.0565344751615</v>
       </c>
       <c r="E75">
-        <v>101.7546</v>
+        <v>103.2748</v>
       </c>
       <c r="F75">
-        <v>110.9746</v>
+        <v>112.4948</v>
       </c>
       <c r="G75">
         <v>12.3</v>
@@ -7437,28 +7437,28 @@
         <v>23</v>
       </c>
       <c r="M75">
-        <v>7.113471860000001</v>
+        <v>7.210916680000001</v>
       </c>
       <c r="N75">
-        <v>15.88652814</v>
+        <v>15.78908332</v>
       </c>
       <c r="O75">
-        <v>2.382979221</v>
+        <v>2.368362498</v>
       </c>
       <c r="P75">
-        <v>13.503548919</v>
+        <v>13.420720822</v>
       </c>
       <c r="Q75">
-        <v>23.103548919</v>
+        <v>23.020720822</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1655992935960157</v>
+        <v>0.1699974018133791</v>
       </c>
       <c r="T75">
-        <v>2.194166133985161</v>
+        <v>2.274719030537979</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.233301607521928</v>
+        <v>3.189608342555415</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08451822447147855</v>
+        <v>0.08455058967203287</v>
       </c>
       <c r="C76">
-        <v>30.86173447516153</v>
+        <v>29.23207366287087</v>
       </c>
       <c r="D76">
-        <v>131.0565344751615</v>
+        <v>130.9470736628709</v>
       </c>
       <c r="E76">
-        <v>103.2748</v>
+        <v>104.795</v>
       </c>
       <c r="F76">
-        <v>112.4948</v>
+        <v>114.015</v>
       </c>
       <c r="G76">
         <v>12.3</v>
@@ -7519,28 +7519,28 @@
         <v>23</v>
       </c>
       <c r="M76">
-        <v>7.210916680000001</v>
+        <v>7.308361500000001</v>
       </c>
       <c r="N76">
-        <v>15.78908332</v>
+        <v>15.6916385</v>
       </c>
       <c r="O76">
-        <v>2.368362498</v>
+        <v>2.353745775</v>
       </c>
       <c r="P76">
-        <v>13.420720822</v>
+        <v>13.337892725</v>
       </c>
       <c r="Q76">
-        <v>23.020720822</v>
+        <v>22.937892725</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1699974018133791</v>
+        <v>0.1747473586881315</v>
       </c>
       <c r="T76">
-        <v>2.274719030537979</v>
+        <v>2.361716158815022</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.189608342555415</v>
+        <v>3.147080231321343</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08455058967203287</v>
+        <v>0.08458295487258718</v>
       </c>
       <c r="C77">
-        <v>29.23207366287087</v>
+        <v>27.60259554533127</v>
       </c>
       <c r="D77">
-        <v>130.9470736628709</v>
+        <v>130.8377955453313</v>
       </c>
       <c r="E77">
-        <v>104.795</v>
+        <v>106.3152</v>
       </c>
       <c r="F77">
-        <v>114.015</v>
+        <v>115.5352</v>
       </c>
       <c r="G77">
         <v>12.3</v>
@@ -7601,28 +7601,28 @@
         <v>23</v>
       </c>
       <c r="M77">
-        <v>7.308361500000001</v>
+        <v>7.405806320000001</v>
       </c>
       <c r="N77">
-        <v>15.6916385</v>
+        <v>15.59419368</v>
       </c>
       <c r="O77">
-        <v>2.353745775</v>
+        <v>2.339129052</v>
       </c>
       <c r="P77">
-        <v>13.337892725</v>
+        <v>13.255064628</v>
       </c>
       <c r="Q77">
-        <v>22.937892725</v>
+        <v>22.855064628</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1747473586881315</v>
+        <v>0.1798931453024466</v>
       </c>
       <c r="T77">
-        <v>2.361716158815022</v>
+        <v>2.455963047781819</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.147080231321343</v>
+        <v>3.10567128090922</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08458295487258718</v>
+        <v>0.08461532007314149</v>
       </c>
       <c r="C78">
-        <v>27.60259554533127</v>
+        <v>25.97329966553617</v>
       </c>
       <c r="D78">
-        <v>130.8377955453313</v>
+        <v>130.7286996655362</v>
       </c>
       <c r="E78">
-        <v>106.3152</v>
+        <v>107.8354</v>
       </c>
       <c r="F78">
-        <v>115.5352</v>
+        <v>117.0554</v>
       </c>
       <c r="G78">
         <v>12.3</v>
@@ -7683,28 +7683,28 @@
         <v>23</v>
       </c>
       <c r="M78">
-        <v>7.405806320000001</v>
+        <v>7.503251140000001</v>
       </c>
       <c r="N78">
-        <v>15.59419368</v>
+        <v>15.49674886</v>
       </c>
       <c r="O78">
-        <v>2.339129052</v>
+        <v>2.324512329</v>
       </c>
       <c r="P78">
-        <v>13.255064628</v>
+        <v>13.172236531</v>
       </c>
       <c r="Q78">
-        <v>22.855064628</v>
+        <v>22.772236531</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1798931453024466</v>
+        <v>0.1854863916223543</v>
       </c>
       <c r="T78">
-        <v>2.455963047781819</v>
+        <v>2.558405318397902</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.10567128090922</v>
+        <v>3.065337887650659</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08461532007314149</v>
+        <v>0.0846476852736958</v>
       </c>
       <c r="C79">
-        <v>25.97329966553617</v>
+        <v>24.3441855680019</v>
       </c>
       <c r="D79">
-        <v>130.7286996655362</v>
+        <v>130.6197855680019</v>
       </c>
       <c r="E79">
-        <v>107.8354</v>
+        <v>109.3556</v>
       </c>
       <c r="F79">
-        <v>117.0554</v>
+        <v>118.5756</v>
       </c>
       <c r="G79">
         <v>12.3</v>
@@ -7765,28 +7765,28 @@
         <v>23</v>
       </c>
       <c r="M79">
-        <v>7.503251140000001</v>
+        <v>7.600695960000001</v>
       </c>
       <c r="N79">
-        <v>15.49674886</v>
+        <v>15.39930404</v>
       </c>
       <c r="O79">
-        <v>2.324512329</v>
+        <v>2.309895606</v>
       </c>
       <c r="P79">
-        <v>13.172236531</v>
+        <v>13.089408434</v>
       </c>
       <c r="Q79">
-        <v>22.772236531</v>
+        <v>22.689408434</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1854863916223543</v>
+        <v>0.1915881148804355</v>
       </c>
       <c r="T79">
-        <v>2.558405318397902</v>
+        <v>2.670160522706357</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.065337887650659</v>
+        <v>3.02603868396283</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0846476852736958</v>
+        <v>0.08991775047425012</v>
       </c>
       <c r="C80">
-        <v>24.3441855680019</v>
+        <v>7.220860317371262</v>
       </c>
       <c r="D80">
-        <v>130.6197855680019</v>
+        <v>115.0166603173713</v>
       </c>
       <c r="E80">
-        <v>109.3556</v>
+        <v>110.8758</v>
       </c>
       <c r="F80">
-        <v>118.5756</v>
+        <v>120.0958</v>
       </c>
       <c r="G80">
         <v>12.3</v>
@@ -7847,45 +7847,45 @@
         <v>23</v>
       </c>
       <c r="M80">
-        <v>7.600695960000001</v>
+        <v>8.634888020000002</v>
       </c>
       <c r="N80">
-        <v>15.39930404</v>
+        <v>14.36511198</v>
       </c>
       <c r="O80">
-        <v>2.309895606</v>
+        <v>2.154766797</v>
       </c>
       <c r="P80">
-        <v>13.089408434</v>
+        <v>12.210345183</v>
       </c>
       <c r="Q80">
-        <v>22.689408434</v>
+        <v>21.810345183</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1915881148804355</v>
+        <v>0.1982709546392863</v>
       </c>
       <c r="T80">
-        <v>2.670160522706357</v>
+        <v>2.792559079806092</v>
       </c>
       <c r="U80">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V80">
         <v>0.15</v>
       </c>
       <c r="W80">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>3.02603868396283</v>
+        <v>2.663613001897388</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08991775047425012</v>
+        <v>0.09001641567480442</v>
       </c>
       <c r="C81">
-        <v>7.220860317371262</v>
+        <v>5.444010345090334</v>
       </c>
       <c r="D81">
-        <v>115.0166603173713</v>
+        <v>114.7600103450904</v>
       </c>
       <c r="E81">
-        <v>110.8758</v>
+        <v>112.396</v>
       </c>
       <c r="F81">
-        <v>120.0958</v>
+        <v>121.616</v>
       </c>
       <c r="G81">
         <v>12.3</v>
@@ -7929,28 +7929,28 @@
         <v>23</v>
       </c>
       <c r="M81">
-        <v>8.634888020000002</v>
+        <v>8.744190400000001</v>
       </c>
       <c r="N81">
-        <v>14.36511198</v>
+        <v>14.2558096</v>
       </c>
       <c r="O81">
-        <v>2.154766797</v>
+        <v>2.13837144</v>
       </c>
       <c r="P81">
-        <v>12.210345183</v>
+        <v>12.11743816</v>
       </c>
       <c r="Q81">
-        <v>21.810345183</v>
+        <v>21.71743816</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1982709546392863</v>
+        <v>0.2056220783740221</v>
       </c>
       <c r="T81">
-        <v>2.792559079806092</v>
+        <v>2.927197492615802</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.663613001897388</v>
+        <v>2.630317839373671</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09001641567480442</v>
+        <v>0.09011508087535874</v>
       </c>
       <c r="C82">
-        <v>5.444010345090334</v>
+        <v>3.668303208182223</v>
       </c>
       <c r="D82">
-        <v>114.7600103450904</v>
+        <v>114.5045032081822</v>
       </c>
       <c r="E82">
-        <v>112.396</v>
+        <v>113.9162</v>
       </c>
       <c r="F82">
-        <v>121.616</v>
+        <v>123.1362</v>
       </c>
       <c r="G82">
         <v>12.3</v>
@@ -8011,28 +8011,28 @@
         <v>23</v>
       </c>
       <c r="M82">
-        <v>8.744190400000001</v>
+        <v>8.853492780000002</v>
       </c>
       <c r="N82">
-        <v>14.2558096</v>
+        <v>14.14650722</v>
       </c>
       <c r="O82">
-        <v>2.13837144</v>
+        <v>2.121976083</v>
       </c>
       <c r="P82">
-        <v>12.11743816</v>
+        <v>12.024531137</v>
       </c>
       <c r="Q82">
-        <v>21.71743816</v>
+        <v>21.624531137</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2056220783740221</v>
+        <v>0.2137470046071513</v>
       </c>
       <c r="T82">
-        <v>2.927197492615802</v>
+        <v>3.076008369931797</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.630317839373671</v>
+        <v>2.597844779628317</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09011508087535874</v>
+        <v>0.09021374607591305</v>
       </c>
       <c r="C83">
-        <v>3.668303208182223</v>
+        <v>1.89373129021574</v>
       </c>
       <c r="D83">
-        <v>114.5045032081822</v>
+        <v>114.2501312902158</v>
       </c>
       <c r="E83">
-        <v>113.9162</v>
+        <v>115.4364</v>
       </c>
       <c r="F83">
-        <v>123.1362</v>
+        <v>124.6564</v>
       </c>
       <c r="G83">
         <v>12.3</v>
@@ -8093,28 +8093,28 @@
         <v>23</v>
       </c>
       <c r="M83">
-        <v>8.853492780000002</v>
+        <v>8.962795160000002</v>
       </c>
       <c r="N83">
-        <v>14.14650722</v>
+        <v>14.03720484</v>
       </c>
       <c r="O83">
-        <v>2.121976083</v>
+        <v>2.105580725999999</v>
       </c>
       <c r="P83">
-        <v>12.024531137</v>
+        <v>11.931624114</v>
       </c>
       <c r="Q83">
-        <v>21.624531137</v>
+        <v>21.531624114</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2137470046071513</v>
+        <v>0.2227747004217392</v>
       </c>
       <c r="T83">
-        <v>3.076008369931797</v>
+        <v>3.241353789171791</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.597844779628317</v>
+        <v>2.56616374573041</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09021374607591305</v>
+        <v>0.09031241127646736</v>
       </c>
       <c r="C84">
-        <v>1.89373129021574</v>
+        <v>0.1202870422892062</v>
       </c>
       <c r="D84">
-        <v>114.2501312902158</v>
+        <v>113.9968870422892</v>
       </c>
       <c r="E84">
-        <v>115.4364</v>
+        <v>116.9566</v>
       </c>
       <c r="F84">
-        <v>124.6564</v>
+        <v>126.1766</v>
       </c>
       <c r="G84">
         <v>12.3</v>
@@ -8175,28 +8175,28 @@
         <v>23</v>
       </c>
       <c r="M84">
-        <v>8.962795160000002</v>
+        <v>9.072097540000001</v>
       </c>
       <c r="N84">
-        <v>14.03720484</v>
+        <v>13.92790246</v>
       </c>
       <c r="O84">
-        <v>2.105580725999999</v>
+        <v>2.089185369</v>
       </c>
       <c r="P84">
-        <v>11.931624114</v>
+        <v>11.838717091</v>
       </c>
       <c r="Q84">
-        <v>21.531624114</v>
+        <v>21.438717091</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2227747004217392</v>
+        <v>0.2328644780968669</v>
       </c>
       <c r="T84">
-        <v>3.241353789171791</v>
+        <v>3.426151610675315</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.56616374573041</v>
+        <v>2.535246110239683</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09031241127646736</v>
+        <v>0.09041107647702168</v>
       </c>
       <c r="C85">
-        <v>0.1202870422892062</v>
+        <v>-1.65203701771614</v>
       </c>
       <c r="D85">
-        <v>113.9968870422892</v>
+        <v>113.7447629822839</v>
       </c>
       <c r="E85">
-        <v>116.9566</v>
+        <v>118.4768</v>
       </c>
       <c r="F85">
-        <v>126.1766</v>
+        <v>127.6968</v>
       </c>
       <c r="G85">
         <v>12.3</v>
@@ -8257,28 +8257,28 @@
         <v>23</v>
       </c>
       <c r="M85">
-        <v>9.072097540000001</v>
+        <v>9.181399920000002</v>
       </c>
       <c r="N85">
-        <v>13.92790246</v>
+        <v>13.81860008</v>
       </c>
       <c r="O85">
-        <v>2.089185369</v>
+        <v>2.072790012</v>
       </c>
       <c r="P85">
-        <v>11.838717091</v>
+        <v>11.745810068</v>
       </c>
       <c r="Q85">
-        <v>21.438717091</v>
+        <v>21.345810068</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2328644780968669</v>
+        <v>0.2442154779813855</v>
       </c>
       <c r="T85">
-        <v>3.426151610675315</v>
+        <v>3.634049159866779</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.535246110239683</v>
+        <v>2.505064608927305</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09041107647702168</v>
+        <v>0.09332749167757598</v>
       </c>
       <c r="C86">
-        <v>-1.652037017716125</v>
+        <v>-10.15192275403474</v>
       </c>
       <c r="D86">
-        <v>113.7447629822839</v>
+        <v>106.7650772459653</v>
       </c>
       <c r="E86">
-        <v>118.4768</v>
+        <v>119.997</v>
       </c>
       <c r="F86">
-        <v>127.6968</v>
+        <v>129.217</v>
       </c>
       <c r="G86">
         <v>12.3</v>
@@ -8339,45 +8339,45 @@
         <v>23</v>
       </c>
       <c r="M86">
-        <v>9.181399920000002</v>
+        <v>9.794648600000002</v>
       </c>
       <c r="N86">
-        <v>13.81860008</v>
+        <v>13.2053514</v>
       </c>
       <c r="O86">
-        <v>2.072790012</v>
+        <v>1.98080271</v>
       </c>
       <c r="P86">
-        <v>11.745810068</v>
+        <v>11.22454869</v>
       </c>
       <c r="Q86">
-        <v>21.345810068</v>
+        <v>20.82454869</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2442154779813854</v>
+        <v>0.2570799445171731</v>
       </c>
       <c r="T86">
-        <v>3.634049159866776</v>
+        <v>3.869666382283768</v>
       </c>
       <c r="U86">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V86">
         <v>0.15</v>
       </c>
       <c r="W86">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.505064608927305</v>
+        <v>2.348221047971031</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09332749167757598</v>
+        <v>0.09345930687813028</v>
       </c>
       <c r="C87">
-        <v>-10.15192275403474</v>
+        <v>-11.96741156520774</v>
       </c>
       <c r="D87">
-        <v>106.7650772459653</v>
+        <v>106.4697884347923</v>
       </c>
       <c r="E87">
-        <v>119.997</v>
+        <v>121.5172</v>
       </c>
       <c r="F87">
-        <v>129.217</v>
+        <v>130.7372</v>
       </c>
       <c r="G87">
         <v>12.3</v>
@@ -8421,28 +8421,28 @@
         <v>23</v>
       </c>
       <c r="M87">
-        <v>9.794648600000002</v>
+        <v>9.909879760000001</v>
       </c>
       <c r="N87">
-        <v>13.2053514</v>
+        <v>13.09012024</v>
       </c>
       <c r="O87">
-        <v>1.98080271</v>
+        <v>1.963518036</v>
       </c>
       <c r="P87">
-        <v>11.22454869</v>
+        <v>11.126602204</v>
       </c>
       <c r="Q87">
-        <v>20.82454869</v>
+        <v>20.726602204</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2570799445171731</v>
+        <v>0.2717821919866449</v>
       </c>
       <c r="T87">
-        <v>3.869666382283768</v>
+        <v>4.138943207903186</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.348221047971031</v>
+        <v>2.320916152064392</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09345930687813028</v>
+        <v>0.09359112207868459</v>
       </c>
       <c r="C88">
-        <v>-11.96741156520774</v>
+        <v>-13.78127147326347</v>
       </c>
       <c r="D88">
-        <v>106.4697884347923</v>
+        <v>106.1761285267365</v>
       </c>
       <c r="E88">
-        <v>121.5172</v>
+        <v>123.0374</v>
       </c>
       <c r="F88">
-        <v>130.7372</v>
+        <v>132.2574</v>
       </c>
       <c r="G88">
         <v>12.3</v>
@@ -8503,28 +8503,28 @@
         <v>23</v>
       </c>
       <c r="M88">
-        <v>9.909879760000001</v>
+        <v>10.02511092</v>
       </c>
       <c r="N88">
-        <v>13.09012024</v>
+        <v>12.97488908</v>
       </c>
       <c r="O88">
-        <v>1.963518036</v>
+        <v>1.946233361999999</v>
       </c>
       <c r="P88">
-        <v>11.126602204</v>
+        <v>11.028655718</v>
       </c>
       <c r="Q88">
-        <v>20.726602204</v>
+        <v>20.628655718</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2717821919866449</v>
+        <v>0.2887463236821892</v>
       </c>
       <c r="T88">
-        <v>4.138943207903186</v>
+        <v>4.449647237464054</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.320916152064392</v>
+        <v>2.294238954914226</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09359112207868459</v>
+        <v>0.09372293727923892</v>
       </c>
       <c r="C89">
-        <v>-13.78127147326347</v>
+        <v>-15.59351591941842</v>
       </c>
       <c r="D89">
-        <v>106.1761285267365</v>
+        <v>105.8840840805816</v>
       </c>
       <c r="E89">
-        <v>123.0374</v>
+        <v>124.5576</v>
       </c>
       <c r="F89">
-        <v>132.2574</v>
+        <v>133.7776</v>
       </c>
       <c r="G89">
         <v>12.3</v>
@@ -8585,28 +8585,28 @@
         <v>23</v>
       </c>
       <c r="M89">
-        <v>10.02511092</v>
+        <v>10.14034208</v>
       </c>
       <c r="N89">
-        <v>12.97488908</v>
+        <v>12.85965792</v>
       </c>
       <c r="O89">
-        <v>1.946233361999999</v>
+        <v>1.928948688</v>
       </c>
       <c r="P89">
-        <v>11.028655718</v>
+        <v>10.930709232</v>
       </c>
       <c r="Q89">
-        <v>20.628655718</v>
+        <v>20.530709232</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2887463236821892</v>
+        <v>0.3085378106603243</v>
       </c>
       <c r="T89">
-        <v>4.449647237464054</v>
+        <v>4.812135271951735</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.294238954914226</v>
+        <v>2.268168057699292</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09372293727923892</v>
+        <v>0.09385475247979322</v>
       </c>
       <c r="C90">
-        <v>-15.59351591941842</v>
+        <v>-17.40415819741081</v>
       </c>
       <c r="D90">
-        <v>105.8840840805816</v>
+        <v>105.5936418025892</v>
       </c>
       <c r="E90">
-        <v>124.5576</v>
+        <v>126.0778</v>
       </c>
       <c r="F90">
-        <v>133.7776</v>
+        <v>135.2978</v>
       </c>
       <c r="G90">
         <v>12.3</v>
@@ -8667,28 +8667,28 @@
         <v>23</v>
       </c>
       <c r="M90">
-        <v>10.14034208</v>
+        <v>10.25557324</v>
       </c>
       <c r="N90">
-        <v>12.85965792</v>
+        <v>12.74442676</v>
       </c>
       <c r="O90">
-        <v>1.928948688</v>
+        <v>1.911664014</v>
       </c>
       <c r="P90">
-        <v>10.930709232</v>
+        <v>10.832762746</v>
       </c>
       <c r="Q90">
-        <v>20.530709232</v>
+        <v>20.432762746</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3085378106603243</v>
+        <v>0.331927749816302</v>
       </c>
       <c r="T90">
-        <v>4.812135271951735</v>
+        <v>5.24053022180081</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.268168057699292</v>
+        <v>2.24268302334312</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09385475247979322</v>
+        <v>0.09398656768034754</v>
       </c>
       <c r="C91">
-        <v>-17.40415819741081</v>
+        <v>-19.21321145551795</v>
       </c>
       <c r="D91">
-        <v>105.5936418025892</v>
+        <v>105.3047885444821</v>
       </c>
       <c r="E91">
-        <v>126.0778</v>
+        <v>127.598</v>
       </c>
       <c r="F91">
-        <v>135.2978</v>
+        <v>136.818</v>
       </c>
       <c r="G91">
         <v>12.3</v>
@@ -8749,28 +8749,28 @@
         <v>23</v>
       </c>
       <c r="M91">
-        <v>10.25557324</v>
+        <v>10.3708044</v>
       </c>
       <c r="N91">
-        <v>12.74442676</v>
+        <v>12.6291956</v>
       </c>
       <c r="O91">
-        <v>1.911664014</v>
+        <v>1.89437934</v>
       </c>
       <c r="P91">
-        <v>10.832762746</v>
+        <v>10.73481626</v>
       </c>
       <c r="Q91">
-        <v>20.432762746</v>
+        <v>20.33481626</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.331927749816302</v>
+        <v>0.3599956768034754</v>
       </c>
       <c r="T91">
-        <v>5.24053022180081</v>
+        <v>5.754604161619702</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.24268302334312</v>
+        <v>2.217764323083752</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09398656768034754</v>
+        <v>0.09411838288090185</v>
       </c>
       <c r="C92">
-        <v>-19.21321145551795</v>
+        <v>-21.02068869854023</v>
       </c>
       <c r="D92">
-        <v>105.3047885444821</v>
+        <v>105.0175113014598</v>
       </c>
       <c r="E92">
-        <v>127.598</v>
+        <v>129.1182</v>
       </c>
       <c r="F92">
-        <v>136.818</v>
+        <v>138.3382</v>
       </c>
       <c r="G92">
         <v>12.3</v>
@@ -8831,28 +8831,28 @@
         <v>23</v>
       </c>
       <c r="M92">
-        <v>10.3708044</v>
+        <v>10.48603556</v>
       </c>
       <c r="N92">
-        <v>12.6291956</v>
+        <v>12.51396444</v>
       </c>
       <c r="O92">
-        <v>1.89437934</v>
+        <v>1.877094666</v>
       </c>
       <c r="P92">
-        <v>10.73481626</v>
+        <v>10.636869774</v>
       </c>
       <c r="Q92">
-        <v>20.33481626</v>
+        <v>20.236869774</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3599956768034754</v>
+        <v>0.3943009208989094</v>
       </c>
       <c r="T92">
-        <v>5.754604161619702</v>
+        <v>6.382916754731681</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.217764323083752</v>
+        <v>2.193393286566348</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09411838288090185</v>
+        <v>0.09425019808145615</v>
       </c>
       <c r="C93">
-        <v>-21.02068869854023</v>
+        <v>-22.82660278975288</v>
       </c>
       <c r="D93">
-        <v>105.0175113014598</v>
+        <v>104.7317972102471</v>
       </c>
       <c r="E93">
-        <v>129.1182</v>
+        <v>130.6384</v>
       </c>
       <c r="F93">
-        <v>138.3382</v>
+        <v>139.8584</v>
       </c>
       <c r="G93">
         <v>12.3</v>
@@ -8913,28 +8913,28 @@
         <v>23</v>
       </c>
       <c r="M93">
-        <v>10.48603556</v>
+        <v>10.60126672</v>
       </c>
       <c r="N93">
-        <v>12.51396444</v>
+        <v>12.39873328</v>
       </c>
       <c r="O93">
-        <v>1.877094666</v>
+        <v>1.859809992</v>
       </c>
       <c r="P93">
-        <v>10.636869774</v>
+        <v>10.538923288</v>
       </c>
       <c r="Q93">
-        <v>20.236869774</v>
+        <v>20.138923288</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3943009208989094</v>
+        <v>0.4371824760182021</v>
       </c>
       <c r="T93">
-        <v>6.382916754731681</v>
+        <v>7.168307496121654</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.193393286566348</v>
+        <v>2.169552055190627</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09425019808145615</v>
+        <v>0.09438201328201046</v>
       </c>
       <c r="C94">
-        <v>-22.82660278975288</v>
+        <v>-24.63096645282594</v>
       </c>
       <c r="D94">
-        <v>104.7317972102471</v>
+        <v>104.4476335471741</v>
       </c>
       <c r="E94">
-        <v>130.6384</v>
+        <v>132.1586</v>
       </c>
       <c r="F94">
-        <v>139.8584</v>
+        <v>141.3786</v>
       </c>
       <c r="G94">
         <v>12.3</v>
@@ -8995,28 +8995,28 @@
         <v>23</v>
       </c>
       <c r="M94">
-        <v>10.60126672</v>
+        <v>10.71649788</v>
       </c>
       <c r="N94">
-        <v>12.39873328</v>
+        <v>12.28350212</v>
       </c>
       <c r="O94">
-        <v>1.859809992</v>
+        <v>1.842525318</v>
       </c>
       <c r="P94">
-        <v>10.538923288</v>
+        <v>10.440976802</v>
       </c>
       <c r="Q94">
-        <v>20.138923288</v>
+        <v>20.040976802</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4371824760182021</v>
+        <v>0.4923159040287212</v>
       </c>
       <c r="T94">
-        <v>7.168307496121654</v>
+        <v>8.178095592194477</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.169552055190627</v>
+        <v>2.146223538468147</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09438201328201046</v>
+        <v>0.09451382848256476</v>
       </c>
       <c r="C95">
-        <v>-24.63096645282594</v>
+        <v>-26.43379227371317</v>
       </c>
       <c r="D95">
-        <v>104.4476335471741</v>
+        <v>104.1650077262869</v>
       </c>
       <c r="E95">
-        <v>132.1586</v>
+        <v>133.6788</v>
       </c>
       <c r="F95">
-        <v>141.3786</v>
+        <v>142.8988</v>
       </c>
       <c r="G95">
         <v>12.3</v>
@@ -9077,28 +9077,28 @@
         <v>23</v>
       </c>
       <c r="M95">
-        <v>10.71649788</v>
+        <v>10.83172904</v>
       </c>
       <c r="N95">
-        <v>12.28350212</v>
+        <v>12.16827096</v>
       </c>
       <c r="O95">
-        <v>1.842525318</v>
+        <v>1.825240644</v>
       </c>
       <c r="P95">
-        <v>10.440976802</v>
+        <v>10.343030316</v>
       </c>
       <c r="Q95">
-        <v>20.040976802</v>
+        <v>19.943030316</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4923159040287212</v>
+        <v>0.5658271413760799</v>
       </c>
       <c r="T95">
-        <v>8.178095592194477</v>
+        <v>9.524479720291575</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.146223538468147</v>
+        <v>2.123391373165294</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09451382848256476</v>
+        <v>0.09464564368311909</v>
       </c>
       <c r="C96">
-        <v>-26.43379227371317</v>
+        <v>-28.23509270251003</v>
       </c>
       <c r="D96">
-        <v>104.1650077262869</v>
+        <v>103.88390729749</v>
       </c>
       <c r="E96">
-        <v>133.6788</v>
+        <v>135.199</v>
       </c>
       <c r="F96">
-        <v>142.8988</v>
+        <v>144.419</v>
       </c>
       <c r="G96">
         <v>12.3</v>
@@ -9159,28 +9159,28 @@
         <v>23</v>
       </c>
       <c r="M96">
-        <v>10.83172904</v>
+        <v>10.9469602</v>
       </c>
       <c r="N96">
-        <v>12.16827096</v>
+        <v>12.0530398</v>
       </c>
       <c r="O96">
-        <v>1.825240644</v>
+        <v>1.80795597</v>
       </c>
       <c r="P96">
-        <v>10.343030316</v>
+        <v>10.24508383</v>
       </c>
       <c r="Q96">
-        <v>19.943030316</v>
+        <v>19.84508383</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5658271413760799</v>
+        <v>0.6687428736623825</v>
       </c>
       <c r="T96">
-        <v>9.524479720291575</v>
+        <v>11.40941749962752</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.123391373165294</v>
+        <v>2.101039885026712</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09464564368311909</v>
+        <v>0.09477745888367339</v>
       </c>
       <c r="C97">
-        <v>-28.23509270251003</v>
+        <v>-30.03488005528199</v>
       </c>
       <c r="D97">
-        <v>103.88390729749</v>
+        <v>103.604319944718</v>
       </c>
       <c r="E97">
-        <v>135.199</v>
+        <v>136.7192</v>
       </c>
       <c r="F97">
-        <v>144.419</v>
+        <v>145.9392</v>
       </c>
       <c r="G97">
         <v>12.3</v>
@@ -9241,28 +9241,28 @@
         <v>23</v>
       </c>
       <c r="M97">
-        <v>10.9469602</v>
+        <v>11.06219136</v>
       </c>
       <c r="N97">
-        <v>12.0530398</v>
+        <v>11.93780864</v>
       </c>
       <c r="O97">
-        <v>1.80795597</v>
+        <v>1.790671296</v>
       </c>
       <c r="P97">
-        <v>10.24508383</v>
+        <v>10.147137344</v>
       </c>
       <c r="Q97">
-        <v>19.84508383</v>
+        <v>19.747137344</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6687428736623825</v>
+        <v>0.8231164720918361</v>
       </c>
       <c r="T97">
-        <v>11.40941749962752</v>
+        <v>14.23682416863142</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.101039885026712</v>
+        <v>2.079154052891017</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09477745888367339</v>
+        <v>0.09490927408422771</v>
       </c>
       <c r="C98">
-        <v>-30.03488005528196</v>
+        <v>-31.83316651586341</v>
       </c>
       <c r="D98">
-        <v>103.604319944718</v>
+        <v>103.3262334841366</v>
       </c>
       <c r="E98">
-        <v>136.7192</v>
+        <v>138.2394</v>
       </c>
       <c r="F98">
-        <v>145.9392</v>
+        <v>147.4594</v>
       </c>
       <c r="G98">
         <v>12.3</v>
@@ -9323,28 +9323,28 @@
         <v>23</v>
       </c>
       <c r="M98">
-        <v>11.06219136</v>
+        <v>11.17742252</v>
       </c>
       <c r="N98">
-        <v>11.93780864</v>
+        <v>11.82257748</v>
       </c>
       <c r="O98">
-        <v>1.790671296</v>
+        <v>1.773386622</v>
       </c>
       <c r="P98">
-        <v>10.147137344</v>
+        <v>10.049190858</v>
       </c>
       <c r="Q98">
-        <v>19.747137344</v>
+        <v>19.649190858</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8231164720918341</v>
+        <v>1.080405802807589</v>
       </c>
       <c r="T98">
-        <v>14.23682416863139</v>
+        <v>18.94916861697121</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.079154052891018</v>
+        <v>2.057719475026162</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09490927408422771</v>
+        <v>0.09504108928478203</v>
       </c>
       <c r="C99">
-        <v>-31.83316651586341</v>
+        <v>-33.62996413762728</v>
       </c>
       <c r="D99">
-        <v>103.3262334841366</v>
+        <v>103.0496358623727</v>
       </c>
       <c r="E99">
-        <v>138.2394</v>
+        <v>139.7596</v>
       </c>
       <c r="F99">
-        <v>147.4594</v>
+        <v>148.9796</v>
       </c>
       <c r="G99">
         <v>12.3</v>
@@ -9405,28 +9405,28 @@
         <v>23</v>
       </c>
       <c r="M99">
-        <v>11.17742252</v>
+        <v>11.29265368</v>
       </c>
       <c r="N99">
-        <v>11.82257748</v>
+        <v>11.70734632</v>
       </c>
       <c r="O99">
-        <v>1.773386622</v>
+        <v>1.756101948</v>
       </c>
       <c r="P99">
-        <v>10.049190858</v>
+        <v>9.951244372</v>
       </c>
       <c r="Q99">
-        <v>19.649190858</v>
+        <v>19.551244372</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.080405802807589</v>
+        <v>1.5949844642391</v>
       </c>
       <c r="T99">
-        <v>18.94916861697121</v>
+        <v>28.37385751365087</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.057719475026162</v>
+        <v>2.036722337525895</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09504108928478203</v>
+        <v>0.09517290448533633</v>
       </c>
       <c r="C100">
-        <v>-33.62996413762728</v>
+        <v>-35.42528484522678</v>
       </c>
       <c r="D100">
-        <v>103.0496358623727</v>
+        <v>102.7745151547732</v>
       </c>
       <c r="E100">
-        <v>139.7596</v>
+        <v>141.2798</v>
       </c>
       <c r="F100">
-        <v>148.9796</v>
+        <v>150.4998</v>
       </c>
       <c r="G100">
         <v>12.3</v>
@@ -9487,28 +9487,28 @@
         <v>23</v>
       </c>
       <c r="M100">
-        <v>11.29265368</v>
+        <v>11.40788484</v>
       </c>
       <c r="N100">
-        <v>11.70734632</v>
+        <v>11.59211516</v>
       </c>
       <c r="O100">
-        <v>1.756101948</v>
+        <v>1.738817273999999</v>
       </c>
       <c r="P100">
-        <v>9.951244372</v>
+        <v>9.853297885999998</v>
       </c>
       <c r="Q100">
-        <v>19.551244372</v>
+        <v>19.453297886</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.5949844642391</v>
+        <v>3.13872044853363</v>
       </c>
       <c r="T100">
-        <v>28.37385751365087</v>
+        <v>56.64792420368983</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.036722337525895</v>
+        <v>2.016149384621593</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09517290448533633</v>
-      </c>
-      <c r="C101">
-        <v>-35.42528484522678</v>
-      </c>
-      <c r="D101">
-        <v>102.7745151547732</v>
-      </c>
-      <c r="E101">
-        <v>141.2798</v>
-      </c>
-      <c r="F101">
-        <v>150.4998</v>
-      </c>
-      <c r="G101">
-        <v>12.3</v>
-      </c>
-      <c r="H101">
-        <v>142.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>32.6</v>
-      </c>
-      <c r="K101">
-        <v>9.600000000000001</v>
-      </c>
-      <c r="L101">
-        <v>23</v>
-      </c>
-      <c r="M101">
-        <v>11.40788484</v>
-      </c>
-      <c r="N101">
-        <v>11.59211516</v>
-      </c>
-      <c r="O101">
-        <v>1.738817273999999</v>
-      </c>
-      <c r="P101">
-        <v>9.853297885999998</v>
-      </c>
-      <c r="Q101">
-        <v>19.453297886</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.13872044853363</v>
-      </c>
-      <c r="T101">
-        <v>56.64792420368983</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.06443</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.016149384621593</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
